--- a/01_Preprocess/01_Filtering/c_data/01_filter.xlsx
+++ b/01_Preprocess/01_Filtering/c_data/01_filter.xlsx
@@ -7,8 +7,9 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="filter_log" sheetId="1" r:id="rId1"/>
-    <sheet name="contaminants_removed" sheetId="2" r:id="rId2"/>
+    <sheet name="overview" sheetId="1" r:id="rId1"/>
+    <sheet name="filter_log" sheetId="2" r:id="rId2"/>
+    <sheet name="contaminants_removed" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -352,93 +353,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>sheet</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>precursors</t>
+          <t>rows</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>protein_groups</t>
+          <t>columns</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>pct_signal</t>
+          <t>description</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>repaired</t>
+          <t>filter_log</t>
         </is>
       </c>
       <c r="B2">
-        <v>53760</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>3736</v>
-      </c>
-      <c r="D2">
-        <v>99.72765070997796</v>
+        <v>4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Precursors, protein groups and share of starting signal after each filter</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>shared peptides removed</t>
+          <t>contaminants_removed</t>
         </is>
       </c>
       <c r="B3">
-        <v>49801</v>
+        <v>211</v>
       </c>
       <c r="C3">
-        <v>3664</v>
-      </c>
-      <c r="D3">
-        <v>85.94764178778486</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>compound groups removed</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>49788</v>
-      </c>
-      <c r="C4">
-        <v>3662</v>
-      </c>
-      <c r="D4">
-        <v>85.94736147006761</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>contaminants removed</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>47133</v>
-      </c>
-      <c r="C5">
-        <v>3451</v>
-      </c>
-      <c r="D5">
-        <v>57.99577454956071</v>
+        <v>4</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Contaminant symbol strings removed, how each matched, and the signal it carried</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -448,6 +421,102 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>precursors</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>protein_groups</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>pct_signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>repaired</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>53760</v>
+      </c>
+      <c r="C2">
+        <v>3736</v>
+      </c>
+      <c r="D2">
+        <v>99.72765070997796</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>shared peptides removed</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>49801</v>
+      </c>
+      <c r="C3">
+        <v>3664</v>
+      </c>
+      <c r="D3">
+        <v>85.94764178778486</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>compound groups removed</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>49788</v>
+      </c>
+      <c r="C4">
+        <v>3662</v>
+      </c>
+      <c r="D4">
+        <v>85.94736147006761</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>contaminants removed</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>47133</v>
+      </c>
+      <c r="C5">
+        <v>3451</v>
+      </c>
+      <c r="D5">
+        <v>57.99577454956071</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D212"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -459,17 +528,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>matched_by</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>precursors</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_signal</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>matched_by</t>
         </is>
       </c>
     </row>
@@ -479,16 +548,16 @@
           <t>HBA1</t>
         </is>
       </c>
-      <c r="B2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C2">
         <v>32</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>9.374270014163059</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -497,16 +566,16 @@
           <t>HBB</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C3">
         <v>29</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>9.309573450617464</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -515,16 +584,16 @@
           <t>ALB</t>
         </is>
       </c>
-      <c r="B4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C4">
         <v>109</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>7.993713901343371</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -533,16 +602,16 @@
           <t>TF</t>
         </is>
       </c>
-      <c r="B5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C5">
         <v>95</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>0.4266460857527949</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -551,16 +620,16 @@
           <t>CA1</t>
         </is>
       </c>
-      <c r="B6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C6">
         <v>34</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>0.3350520869841229</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -569,16 +638,16 @@
           <t>HBD</t>
         </is>
       </c>
-      <c r="B7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C7">
         <v>19</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>0.1199342157231878</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -587,16 +656,16 @@
           <t>SERPINA1</t>
         </is>
       </c>
-      <c r="B8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C8">
         <v>45</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>0.06221858287038758</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -605,16 +674,16 @@
           <t>IGHG1</t>
         </is>
       </c>
-      <c r="B9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C9">
         <v>15</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>0.05415335788973432</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="10">
@@ -623,16 +692,16 @@
           <t>APOA1</t>
         </is>
       </c>
-      <c r="B10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C10">
         <v>46</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>0.04225927799299053</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="11">
@@ -641,16 +710,16 @@
           <t>IGKC</t>
         </is>
       </c>
-      <c r="B11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C11">
         <v>13</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>0.03930751400690437</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="12">
@@ -659,16 +728,16 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="B12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C12">
         <v>142</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>0.02298117744098634</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="13">
@@ -677,16 +746,16 @@
           <t>HP</t>
         </is>
       </c>
-      <c r="B13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C13">
         <v>23</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>0.01501147052513072</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="14">
@@ -695,16 +764,16 @@
           <t>HPX</t>
         </is>
       </c>
-      <c r="B14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C14">
         <v>31</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>0.0103701174757759</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="15">
@@ -713,16 +782,16 @@
           <t>SERPINC1</t>
         </is>
       </c>
-      <c r="B15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C15">
         <v>32</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>0.01033148577418564</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="16">
@@ -731,16 +800,16 @@
           <t>ORM1</t>
         </is>
       </c>
-      <c r="B16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C16">
         <v>13</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>0.009807999274047628</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="17">
@@ -749,16 +818,16 @@
           <t>FGG</t>
         </is>
       </c>
-      <c r="B17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C17">
         <v>37</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>0.008699852962568731</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="18">
@@ -767,16 +836,16 @@
           <t>IGHG2</t>
         </is>
       </c>
-      <c r="B18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C18">
         <v>11</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>0.007790058804980808</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="19">
@@ -785,16 +854,16 @@
           <t>APOA2</t>
         </is>
       </c>
-      <c r="B19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C19">
         <v>8</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>0.007561882310911638</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="20">
@@ -803,16 +872,16 @@
           <t>IGHM</t>
         </is>
       </c>
-      <c r="B20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C20">
         <v>31</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>0.007498092111904506</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="21">
@@ -821,16 +890,16 @@
           <t>SLC4A1</t>
         </is>
       </c>
-      <c r="B21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C21">
         <v>42</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>0.00747469734141741</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="22">
@@ -839,16 +908,16 @@
           <t>IGHA1</t>
         </is>
       </c>
-      <c r="B22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C22">
         <v>15</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>0.007439431780256917</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="23">
@@ -857,16 +926,16 @@
           <t>AHSG</t>
         </is>
       </c>
-      <c r="B23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C23">
         <v>14</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>0.006134026491755945</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="24">
@@ -875,16 +944,16 @@
           <t>FGA</t>
         </is>
       </c>
-      <c r="B24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C24">
         <v>55</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>0.005515902392758371</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="25">
@@ -893,16 +962,16 @@
           <t>KRT1</t>
         </is>
       </c>
-      <c r="B25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C25">
         <v>30</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>0.005014085892895379</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="26">
@@ -911,16 +980,16 @@
           <t>GC</t>
         </is>
       </c>
-      <c r="B26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C26">
         <v>39</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>0.004603217719664348</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="27">
@@ -929,16 +998,16 @@
           <t>APOA4</t>
         </is>
       </c>
-      <c r="B27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C27">
         <v>39</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>0.004063631705592294</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="28">
@@ -947,16 +1016,16 @@
           <t>FGB</t>
         </is>
       </c>
-      <c r="B28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C28">
         <v>41</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>0.003998836383976705</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="29">
@@ -965,16 +1034,16 @@
           <t>HBG1</t>
         </is>
       </c>
-      <c r="B29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C29">
         <v>4</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>0.00348057202198938</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="30">
@@ -983,16 +1052,16 @@
           <t>TTR</t>
         </is>
       </c>
-      <c r="B30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C30">
         <v>8</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>0.003380990843588053</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="31">
@@ -1001,16 +1070,16 @@
           <t>CFH</t>
         </is>
       </c>
-      <c r="B31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C31">
         <v>58</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>0.002537927158004708</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="32">
@@ -1019,16 +1088,16 @@
           <t>CP</t>
         </is>
       </c>
-      <c r="B32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C32">
         <v>51</v>
       </c>
-      <c r="C32">
+      <c r="D32">
         <v>0.002413350320819479</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="33">
@@ -1037,16 +1106,16 @@
           <t>APOB</t>
         </is>
       </c>
-      <c r="B33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C33">
         <v>172</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>0.002337498769986352</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="34">
@@ -1055,16 +1124,16 @@
           <t>SPTA1</t>
         </is>
       </c>
-      <c r="B34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C34">
         <v>132</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>0.002239015625199535</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="35">
@@ -1073,16 +1142,16 @@
           <t>SERPINA3</t>
         </is>
       </c>
-      <c r="B35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C35">
         <v>21</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>0.002191285812433823</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="36">
@@ -1091,16 +1160,16 @@
           <t>IGHG3</t>
         </is>
       </c>
-      <c r="B36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C36">
         <v>10</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>0.002033071723152557</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="37">
@@ -1109,16 +1178,16 @@
           <t>APOH</t>
         </is>
       </c>
-      <c r="B37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C37">
         <v>15</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>0.001834766275260182</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="38">
@@ -1127,16 +1196,16 @@
           <t>KRT10</t>
         </is>
       </c>
-      <c r="B38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C38">
         <v>19</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>0.001782338284746402</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="39">
@@ -1145,16 +1214,16 @@
           <t>ORM2</t>
         </is>
       </c>
-      <c r="B39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C39">
         <v>13</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>0.001646384865907391</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="40">
@@ -1163,16 +1232,16 @@
           <t>KRT9</t>
         </is>
       </c>
-      <c r="B40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C40">
         <v>20</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>0.001645079464815833</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="41">
@@ -1181,16 +1250,16 @@
           <t>KNG1</t>
         </is>
       </c>
-      <c r="B41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C41">
         <v>25</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>0.001468869276874552</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="42">
@@ -1199,16 +1268,16 @@
           <t>CFB</t>
         </is>
       </c>
-      <c r="B42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C42">
         <v>24</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>0.001240903432682277</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="43">
@@ -1217,16 +1286,16 @@
           <t>A1BG</t>
         </is>
       </c>
-      <c r="B43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C43">
         <v>18</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>0.001232933299526316</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="44">
@@ -1235,16 +1304,16 @@
           <t>VTN</t>
         </is>
       </c>
-      <c r="B44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C44">
         <v>19</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>0.001191989831939855</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="45">
@@ -1253,16 +1322,16 @@
           <t>PLG</t>
         </is>
       </c>
-      <c r="B45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C45">
         <v>34</v>
       </c>
-      <c r="C45">
+      <c r="D45">
         <v>0.001010500746058517</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="46">
@@ -1271,16 +1340,16 @@
           <t>AZGP1</t>
         </is>
       </c>
-      <c r="B46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C46">
         <v>18</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>0.001001214781409178</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="47">
@@ -1289,16 +1358,16 @@
           <t>APOD</t>
         </is>
       </c>
-      <c r="B47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C47">
         <v>11</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>0.0009383933459322968</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="48">
@@ -1307,16 +1376,16 @@
           <t>S100A9</t>
         </is>
       </c>
-      <c r="B48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C48">
         <v>14</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>0.0009272617464771614</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="49">
@@ -1325,16 +1394,16 @@
           <t>S100A8</t>
         </is>
       </c>
-      <c r="B49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C49">
         <v>8</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>0.0007956161441063045</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="50">
@@ -1343,16 +1412,16 @@
           <t>SERPING1</t>
         </is>
       </c>
-      <c r="B50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C50">
         <v>23</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>0.000791029710104409</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="51">
@@ -1361,16 +1430,16 @@
           <t>IGHG4</t>
         </is>
       </c>
-      <c r="B51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C51">
         <v>17</v>
       </c>
-      <c r="C51">
+      <c r="D51">
         <v>0.0006932187224934446</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="52">
@@ -1379,16 +1448,16 @@
           <t>F2</t>
         </is>
       </c>
-      <c r="B52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C52">
         <v>25</v>
       </c>
-      <c r="C52">
+      <c r="D52">
         <v>0.0006737684627318644</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="53">
@@ -1397,16 +1466,16 @@
           <t>CLU</t>
         </is>
       </c>
-      <c r="B53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C53">
         <v>14</v>
       </c>
-      <c r="C53">
+      <c r="D53">
         <v>0.0006578039618210681</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="54">
@@ -1415,16 +1484,16 @@
           <t>IGKV3-20</t>
         </is>
       </c>
-      <c r="B54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C54">
         <v>2</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <v>0.0005782967409743913</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="55">
@@ -1433,16 +1502,16 @@
           <t>HBG2</t>
         </is>
       </c>
-      <c r="B55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C55">
         <v>3</v>
       </c>
-      <c r="C55">
+      <c r="D55">
         <v>0.0004339577852901589</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="56">
@@ -1451,16 +1520,16 @@
           <t>APOC3</t>
         </is>
       </c>
-      <c r="B56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C56">
         <v>5</v>
       </c>
-      <c r="C56">
+      <c r="D56">
         <v>0.0004094257590121949</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="57">
@@ -1469,16 +1538,16 @@
           <t>IGLL5</t>
         </is>
       </c>
-      <c r="B57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C57">
         <v>2</v>
       </c>
-      <c r="C57">
+      <c r="D57">
         <v>0.0004083463235333115</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="58">
@@ -1487,16 +1556,16 @@
           <t>EPB42</t>
         </is>
       </c>
-      <c r="B58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C58">
         <v>22</v>
       </c>
-      <c r="C58">
+      <c r="D58">
         <v>0.0003756426650034072</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="59">
@@ -1505,16 +1574,16 @@
           <t>AGT</t>
         </is>
       </c>
-      <c r="B59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C59">
         <v>13</v>
       </c>
-      <c r="C59">
+      <c r="D59">
         <v>0.000374833726376505</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="60">
@@ -1523,16 +1592,16 @@
           <t>SERPIND1</t>
         </is>
       </c>
-      <c r="B60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C60">
         <v>13</v>
       </c>
-      <c r="C60">
+      <c r="D60">
         <v>0.0003270184714528119</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="61">
@@ -1541,16 +1610,16 @@
           <t>ITIH1</t>
         </is>
       </c>
-      <c r="B61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C61">
         <v>23</v>
       </c>
-      <c r="C61">
+      <c r="D61">
         <v>0.0003201661793300259</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="62">
@@ -1559,16 +1628,16 @@
           <t>RBP4</t>
         </is>
       </c>
-      <c r="B62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C62">
         <v>4</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>0.0002823627529578066</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="63">
@@ -1577,16 +1646,16 @@
           <t>LTF</t>
         </is>
       </c>
-      <c r="B63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C63">
         <v>19</v>
       </c>
-      <c r="C63">
+      <c r="D63">
         <v>0.0002629895570348505</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="64">
@@ -1595,16 +1664,16 @@
           <t>APCS</t>
         </is>
       </c>
-      <c r="B64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C64">
         <v>6</v>
       </c>
-      <c r="C64">
+      <c r="D64">
         <v>0.0002509896382258545</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="65">
@@ -1613,16 +1682,16 @@
           <t>APOE</t>
         </is>
       </c>
-      <c r="B65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C65">
         <v>18</v>
       </c>
-      <c r="C65">
+      <c r="D65">
         <v>0.0002505779431369578</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="66">
@@ -1631,16 +1700,16 @@
           <t>HRG</t>
         </is>
       </c>
-      <c r="B66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C66">
         <v>19</v>
       </c>
-      <c r="C66">
+      <c r="D66">
         <v>0.0002232877043689364</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="67">
@@ -1649,16 +1718,16 @@
           <t>C4BPA</t>
         </is>
       </c>
-      <c r="B67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C67">
         <v>23</v>
       </c>
-      <c r="C67">
+      <c r="D67">
         <v>0.0002183260345311721</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="68">
@@ -1667,16 +1736,16 @@
           <t>IGHV3-7</t>
         </is>
       </c>
-      <c r="B68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C68">
         <v>2</v>
       </c>
-      <c r="C68">
+      <c r="D68">
         <v>0.0002173499917511125</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="69">
@@ -1685,16 +1754,16 @@
           <t>IGKV4-1</t>
         </is>
       </c>
-      <c r="B69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C69">
         <v>3</v>
       </c>
-      <c r="C69">
+      <c r="D69">
         <v>0.0002164779163283302</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="70">
@@ -1703,16 +1772,16 @@
           <t>AMBP</t>
         </is>
       </c>
-      <c r="B70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C70">
         <v>13</v>
       </c>
-      <c r="C70">
+      <c r="D70">
         <v>0.000215681542256589</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="71">
@@ -1721,16 +1790,16 @@
           <t>APOC2</t>
         </is>
       </c>
-      <c r="B71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C71">
         <v>4</v>
       </c>
-      <c r="C71">
+      <c r="D71">
         <v>0.0002063505586354428</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="72">
@@ -1739,16 +1808,16 @@
           <t>CLEC3B</t>
         </is>
       </c>
-      <c r="B72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C72">
         <v>9</v>
       </c>
-      <c r="C72">
+      <c r="D72">
         <v>0.000189705010360836</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="73">
@@ -1757,16 +1826,16 @@
           <t>LRG1</t>
         </is>
       </c>
-      <c r="B73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C73">
         <v>9</v>
       </c>
-      <c r="C73">
+      <c r="D73">
         <v>0.0001873315411183386</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="74">
@@ -1775,16 +1844,16 @@
           <t>KRT2</t>
         </is>
       </c>
-      <c r="B74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C74">
         <v>12</v>
       </c>
-      <c r="C74">
+      <c r="D74">
         <v>0.0001804247149543651</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="75">
@@ -1793,16 +1862,16 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="B75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C75">
         <v>15</v>
       </c>
-      <c r="C75">
+      <c r="D75">
         <v>0.0001607825038213726</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="76">
@@ -1811,16 +1880,16 @@
           <t>AFM</t>
         </is>
       </c>
-      <c r="B76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C76">
         <v>18</v>
       </c>
-      <c r="C76">
+      <c r="D76">
         <v>0.0001558875631464072</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="77">
@@ -1829,16 +1898,16 @@
           <t>GYPC</t>
         </is>
       </c>
-      <c r="B77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C77">
         <v>2</v>
       </c>
-      <c r="C77">
+      <c r="D77">
         <v>0.0001550807393008314</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="78">
@@ -1847,16 +1916,16 @@
           <t>JCHAIN</t>
         </is>
       </c>
-      <c r="B78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C78">
         <v>5</v>
       </c>
-      <c r="C78">
+      <c r="D78">
         <v>0.0001514462196438862</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="79">
@@ -1865,16 +1934,16 @@
           <t>F13A1</t>
         </is>
       </c>
-      <c r="B79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C79">
         <v>21</v>
       </c>
-      <c r="C79">
+      <c r="D79">
         <v>0.0001454801711531587</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="80">
@@ -1883,16 +1952,16 @@
           <t>PPBP</t>
         </is>
       </c>
-      <c r="B80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C80">
         <v>6</v>
       </c>
-      <c r="C80">
+      <c r="D80">
         <v>0.0001419321552890717</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="81">
@@ -1901,16 +1970,16 @@
           <t>HBZ</t>
         </is>
       </c>
-      <c r="B81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C81">
         <v>10</v>
       </c>
-      <c r="C81">
+      <c r="D81">
         <v>0.0001411022614397535</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="82">
@@ -1919,16 +1988,16 @@
           <t>SERPINF2</t>
         </is>
       </c>
-      <c r="B82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C82">
         <v>12</v>
       </c>
-      <c r="C82">
+      <c r="D82">
         <v>0.0001409149546363809</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="83">
@@ -1937,16 +2006,16 @@
           <t>C9</t>
         </is>
       </c>
-      <c r="B83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C83">
         <v>12</v>
       </c>
-      <c r="C83">
+      <c r="D83">
         <v>0.0001385513932496654</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="84">
@@ -1955,16 +2024,16 @@
           <t>ARHGDIB</t>
         </is>
       </c>
-      <c r="B84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C84">
         <v>8</v>
       </c>
-      <c r="C84">
+      <c r="D84">
         <v>0.0001272885747710419</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="85">
@@ -1973,16 +2042,16 @@
           <t>AHSP</t>
         </is>
       </c>
-      <c r="B85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C85">
         <v>7</v>
       </c>
-      <c r="C85">
+      <c r="D85">
         <v>0.0001130142413913457</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="86">
@@ -1991,16 +2060,16 @@
           <t>IGHD</t>
         </is>
       </c>
-      <c r="B86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C86">
         <v>10</v>
       </c>
-      <c r="C86">
+      <c r="D86">
         <v>0.0001041345727822492</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="87">
@@ -2009,16 +2078,16 @@
           <t>IGHV4-28</t>
         </is>
       </c>
-      <c r="B87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C87">
         <v>3</v>
       </c>
-      <c r="C87">
+      <c r="D87">
         <v>9.64396158534993E-05</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="88">
@@ -2027,16 +2096,16 @@
           <t>C1QB</t>
         </is>
       </c>
-      <c r="B88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C88">
         <v>7</v>
       </c>
-      <c r="C88">
+      <c r="D88">
         <v>9.523557954613374E-05</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="89">
@@ -2045,16 +2114,16 @@
           <t>APOC1</t>
         </is>
       </c>
-      <c r="B89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C89">
         <v>5</v>
       </c>
-      <c r="C89">
+      <c r="D89">
         <v>9.10129048377717E-05</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="90">
@@ -2063,16 +2132,16 @@
           <t>CTSG</t>
         </is>
       </c>
-      <c r="B90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C90">
         <v>5</v>
       </c>
-      <c r="C90">
+      <c r="D90">
         <v>7.817773255461184E-05</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="91">
@@ -2081,16 +2150,16 @@
           <t>LYZ</t>
         </is>
       </c>
-      <c r="B91">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C91">
         <v>3</v>
       </c>
-      <c r="C91">
+      <c r="D91">
         <v>7.771185885098649E-05</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="92">
@@ -2099,16 +2168,16 @@
           <t>IGHV6-1</t>
         </is>
       </c>
-      <c r="B92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C92">
         <v>2</v>
       </c>
-      <c r="C92">
+      <c r="D92">
         <v>7.513971851431978E-05</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="93">
@@ -2117,16 +2186,16 @@
           <t>IGKV1-5</t>
         </is>
       </c>
-      <c r="B93">
-        <v>1</v>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="D93">
         <v>7.004591332124703E-05</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="94">
@@ -2135,16 +2204,16 @@
           <t>PGLYRP2</t>
         </is>
       </c>
-      <c r="B94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C94">
         <v>9</v>
       </c>
-      <c r="C94">
+      <c r="D94">
         <v>6.668893399642917E-05</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="95">
@@ -2153,16 +2222,16 @@
           <t>IGHA2</t>
         </is>
       </c>
-      <c r="B95">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C95">
         <v>5</v>
       </c>
-      <c r="C95">
+      <c r="D95">
         <v>6.542201774960212E-05</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="96">
@@ -2171,16 +2240,16 @@
           <t>PON1</t>
         </is>
       </c>
-      <c r="B96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C96">
         <v>7</v>
       </c>
-      <c r="C96">
+      <c r="D96">
         <v>6.291555747429884E-05</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="97">
@@ -2189,16 +2258,16 @@
           <t>MPP1</t>
         </is>
       </c>
-      <c r="B97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C97">
         <v>10</v>
       </c>
-      <c r="C97">
+      <c r="D97">
         <v>6.193645376082351E-05</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="98">
@@ -2207,16 +2276,16 @@
           <t>LCP1</t>
         </is>
       </c>
-      <c r="B98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C98">
         <v>11</v>
       </c>
-      <c r="C98">
+      <c r="D98">
         <v>5.852345063767268E-05</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="99">
@@ -2225,16 +2294,16 @@
           <t>TUBB1</t>
         </is>
       </c>
-      <c r="B99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C99">
         <v>4</v>
       </c>
-      <c r="C99">
+      <c r="D99">
         <v>5.016058278228058E-05</v>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="100">
@@ -2243,16 +2312,16 @@
           <t>C1S</t>
         </is>
       </c>
-      <c r="B100">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C100">
         <v>14</v>
       </c>
-      <c r="C100">
+      <c r="D100">
         <v>4.943588843717016E-05</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="101">
@@ -2261,16 +2330,16 @@
           <t>IGKV3D-20</t>
         </is>
       </c>
-      <c r="B101">
-        <v>1</v>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="D101">
         <v>4.650255182482494E-05</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="102">
@@ -2279,16 +2348,16 @@
           <t>DMTN</t>
         </is>
       </c>
-      <c r="B102">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C102">
         <v>11</v>
       </c>
-      <c r="C102">
+      <c r="D102">
         <v>4.44519374781544E-05</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="103">
@@ -2297,16 +2366,16 @@
           <t>C1QC</t>
         </is>
       </c>
-      <c r="B103">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C103">
         <v>6</v>
       </c>
-      <c r="C103">
+      <c r="D103">
         <v>4.442823822944266E-05</v>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="104">
@@ -2315,16 +2384,16 @@
           <t>C4A</t>
         </is>
       </c>
-      <c r="B104">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C104">
         <v>5</v>
       </c>
-      <c r="C104">
+      <c r="D104">
         <v>4.354312018243678E-05</v>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="105">
@@ -2333,16 +2402,16 @@
           <t>CFD</t>
         </is>
       </c>
-      <c r="B105">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C105">
         <v>9</v>
       </c>
-      <c r="C105">
+      <c r="D105">
         <v>4.200370428700651E-05</v>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="106">
@@ -2351,16 +2420,16 @@
           <t>C6</t>
         </is>
       </c>
-      <c r="B106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C106">
         <v>12</v>
       </c>
-      <c r="C106">
+      <c r="D106">
         <v>4.119660402117848E-05</v>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="107">
@@ -2369,16 +2438,16 @@
           <t>IGLV1-47</t>
         </is>
       </c>
-      <c r="B107">
-        <v>1</v>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C107">
+        <v>1</v>
+      </c>
+      <c r="D107">
         <v>4.040829661578678E-05</v>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="108">
@@ -2387,16 +2456,16 @@
           <t>BCAM</t>
         </is>
       </c>
-      <c r="B108">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C108">
         <v>16</v>
       </c>
-      <c r="C108">
+      <c r="D108">
         <v>3.945497178149089E-05</v>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="109">
@@ -2405,16 +2474,16 @@
           <t>IGHV2-70D</t>
         </is>
       </c>
-      <c r="B109">
-        <v>1</v>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C109">
+        <v>1</v>
+      </c>
+      <c r="D109">
         <v>3.78828536968073E-05</v>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="110">
@@ -2423,16 +2492,16 @@
           <t>IGLV3-21</t>
         </is>
       </c>
-      <c r="B110">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C110">
         <v>3</v>
       </c>
-      <c r="C110">
+      <c r="D110">
         <v>3.765870190835708E-05</v>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="111">
@@ -2441,16 +2510,16 @@
           <t>HPR</t>
         </is>
       </c>
-      <c r="B111">
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C111">
         <v>6</v>
       </c>
-      <c r="C111">
+      <c r="D111">
         <v>3.451857564170755E-05</v>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="112">
@@ -2459,16 +2528,16 @@
           <t>HBQ1</t>
         </is>
       </c>
-      <c r="B112">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C112">
         <v>7</v>
       </c>
-      <c r="C112">
+      <c r="D112">
         <v>3.149743231701006E-05</v>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="113">
@@ -2477,16 +2546,16 @@
           <t>PZP</t>
         </is>
       </c>
-      <c r="B113">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C113">
         <v>21</v>
       </c>
-      <c r="C113">
+      <c r="D113">
         <v>3.128751431547318E-05</v>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="114">
@@ -2495,16 +2564,16 @@
           <t>C2</t>
         </is>
       </c>
-      <c r="B114">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C114">
         <v>12</v>
       </c>
-      <c r="C114">
+      <c r="D114">
         <v>2.970220902817708E-05</v>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="115">
@@ -2513,16 +2582,16 @@
           <t>APOM</t>
         </is>
       </c>
-      <c r="B115">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C115">
         <v>5</v>
       </c>
-      <c r="C115">
+      <c r="D115">
         <v>2.903610957459397E-05</v>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="116">
@@ -2531,16 +2600,16 @@
           <t>SERPINA4</t>
         </is>
       </c>
-      <c r="B116">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C116">
         <v>4</v>
       </c>
-      <c r="C116">
+      <c r="D116">
         <v>2.874303911207777E-05</v>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="117">
@@ -2549,16 +2618,16 @@
           <t>IGHV3-72</t>
         </is>
       </c>
-      <c r="B117">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C117">
         <v>2</v>
       </c>
-      <c r="C117">
+      <c r="D117">
         <v>2.578047386948604E-05</v>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="118">
@@ -2567,16 +2636,16 @@
           <t>KLKB1</t>
         </is>
       </c>
-      <c r="B118">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C118">
         <v>13</v>
       </c>
-      <c r="C118">
+      <c r="D118">
         <v>2.329168268627906E-05</v>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="119">
@@ -2585,16 +2654,16 @@
           <t>CFI</t>
         </is>
       </c>
-      <c r="B119">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C119">
         <v>11</v>
       </c>
-      <c r="C119">
+      <c r="D119">
         <v>2.324858102434939E-05</v>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="120">
@@ -2603,16 +2672,16 @@
           <t>PF4</t>
         </is>
       </c>
-      <c r="B120">
-        <v>1</v>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
       </c>
       <c r="C120">
+        <v>1</v>
+      </c>
+      <c r="D120">
         <v>2.289941702076588E-05</v>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="121">
@@ -2621,16 +2690,16 @@
           <t>C8A</t>
         </is>
       </c>
-      <c r="B121">
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C121">
         <v>10</v>
       </c>
-      <c r="C121">
+      <c r="D121">
         <v>2.088487587404509E-05</v>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="122">
@@ -2639,16 +2708,16 @@
           <t>IGLV1-51</t>
         </is>
       </c>
-      <c r="B122">
-        <v>1</v>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C122">
+        <v>1</v>
+      </c>
+      <c r="D122">
         <v>2.085691075353142E-05</v>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="123">
@@ -2657,16 +2726,16 @@
           <t>C1R</t>
         </is>
       </c>
-      <c r="B123">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C123">
         <v>12</v>
       </c>
-      <c r="C123">
+      <c r="D123">
         <v>2.070895554693901E-05</v>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="124">
@@ -2675,16 +2744,16 @@
           <t>IGHV3-64D</t>
         </is>
       </c>
-      <c r="B124">
-        <v>1</v>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C124">
+        <v>1</v>
+      </c>
+      <c r="D124">
         <v>2.059654770282671E-05</v>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="125">
@@ -2693,16 +2762,16 @@
           <t>SERPINA6</t>
         </is>
       </c>
-      <c r="B125">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C125">
         <v>4</v>
       </c>
-      <c r="C125">
+      <c r="D125">
         <v>1.935742594159559E-05</v>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="126">
@@ -2711,16 +2780,16 @@
           <t>IGHV3-15</t>
         </is>
       </c>
-      <c r="B126">
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C126">
         <v>3</v>
       </c>
-      <c r="C126">
+      <c r="D126">
         <v>1.908498349180372E-05</v>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="127">
@@ -2729,16 +2798,16 @@
           <t>IGHV3-35</t>
         </is>
       </c>
-      <c r="B127">
-        <v>1</v>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C127">
+        <v>1</v>
+      </c>
+      <c r="D127">
         <v>1.85613150649075E-05</v>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="128">
@@ -2747,16 +2816,16 @@
           <t>SAA4</t>
         </is>
       </c>
-      <c r="B128">
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C128">
         <v>4</v>
       </c>
-      <c r="C128">
+      <c r="D128">
         <v>1.723447555154927E-05</v>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="129">
@@ -2765,16 +2834,16 @@
           <t>APOL1</t>
         </is>
       </c>
-      <c r="B129">
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C129">
         <v>4</v>
       </c>
-      <c r="C129">
+      <c r="D129">
         <v>1.630028557768283E-05</v>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="130">
@@ -2783,16 +2852,16 @@
           <t>C8G</t>
         </is>
       </c>
-      <c r="B130">
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C130">
         <v>3</v>
       </c>
-      <c r="C130">
+      <c r="D130">
         <v>1.401422267411308E-05</v>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="131">
@@ -2801,16 +2870,16 @@
           <t>VWF</t>
         </is>
       </c>
-      <c r="B131">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C131">
         <v>13</v>
       </c>
-      <c r="C131">
+      <c r="D131">
         <v>1.344505391619816E-05</v>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="132">
@@ -2819,16 +2888,16 @@
           <t>CPN2</t>
         </is>
       </c>
-      <c r="B132">
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C132">
         <v>5</v>
       </c>
-      <c r="C132">
+      <c r="D132">
         <v>1.306506335135736E-05</v>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="133">
@@ -2837,16 +2906,16 @@
           <t>DCD</t>
         </is>
       </c>
-      <c r="B133">
-        <v>1</v>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
       </c>
       <c r="C133">
+        <v>1</v>
+      </c>
+      <c r="D133">
         <v>1.266819119246734E-05</v>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="134">
@@ -2855,16 +2924,16 @@
           <t>PROS1</t>
         </is>
       </c>
-      <c r="B134">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C134">
         <v>7</v>
       </c>
-      <c r="C134">
+      <c r="D134">
         <v>1.158147124246619E-05</v>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="135">
@@ -2873,16 +2942,16 @@
           <t>C8B</t>
         </is>
       </c>
-      <c r="B135">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C135">
         <v>13</v>
       </c>
-      <c r="C135">
+      <c r="D135">
         <v>1.144188587122606E-05</v>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="136">
@@ -2891,16 +2960,16 @@
           <t>IGLV1-40</t>
         </is>
       </c>
-      <c r="B136">
-        <v>1</v>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C136">
+        <v>1</v>
+      </c>
+      <c r="D136">
         <v>1.083792295211038E-05</v>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="137">
@@ -2909,16 +2978,16 @@
           <t>IGLV3-19</t>
         </is>
       </c>
-      <c r="B137">
-        <v>1</v>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C137">
+        <v>1</v>
+      </c>
+      <c r="D137">
         <v>1.033024365328475E-05</v>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="138">
@@ -2927,16 +2996,16 @@
           <t>IGLV2-14</t>
         </is>
       </c>
-      <c r="B138">
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C138">
         <v>2</v>
       </c>
-      <c r="C138">
+      <c r="D138">
         <v>9.626155750958738E-06</v>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="139">
@@ -2945,16 +3014,16 @@
           <t>C4B</t>
         </is>
       </c>
-      <c r="B139">
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C139">
         <v>4</v>
       </c>
-      <c r="C139">
+      <c r="D139">
         <v>9.614427287926634E-06</v>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="140">
@@ -2963,16 +3032,16 @@
           <t>ITIH3</t>
         </is>
       </c>
-      <c r="B140">
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C140">
         <v>4</v>
       </c>
-      <c r="C140">
+      <c r="D140">
         <v>9.331406724548283E-06</v>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="141">
@@ -2981,16 +3050,16 @@
           <t>IGHV3-49</t>
         </is>
       </c>
-      <c r="B141">
-        <v>1</v>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C141">
+        <v>1</v>
+      </c>
+      <c r="D141">
         <v>9.121017103966292E-06</v>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="142">
@@ -2999,16 +3068,16 @@
           <t>IGHV5-51</t>
         </is>
       </c>
-      <c r="B142">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C142">
         <v>2</v>
       </c>
-      <c r="C142">
+      <c r="D142">
         <v>8.984595170597851E-06</v>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="143">
@@ -3017,16 +3086,16 @@
           <t>FERMT3</t>
         </is>
       </c>
-      <c r="B143">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C143">
         <v>4</v>
       </c>
-      <c r="C143">
+      <c r="D143">
         <v>8.865393434196972E-06</v>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="144">
@@ -3035,16 +3104,16 @@
           <t>APOL2</t>
         </is>
       </c>
-      <c r="B144">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C144">
         <v>6</v>
       </c>
-      <c r="C144">
+      <c r="D144">
         <v>8.815674133891087E-06</v>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="145">
@@ -3053,16 +3122,16 @@
           <t>IGHV3-13</t>
         </is>
       </c>
-      <c r="B145">
-        <v>1</v>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C145">
+        <v>1</v>
+      </c>
+      <c r="D145">
         <v>8.408002308489205E-06</v>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="146">
@@ -3071,16 +3140,16 @@
           <t>IGKV3D-15</t>
         </is>
       </c>
-      <c r="B146">
-        <v>1</v>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C146">
+        <v>1</v>
+      </c>
+      <c r="D146">
         <v>8.289605473908716E-06</v>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="147">
@@ -3089,16 +3158,16 @@
           <t>FCN3</t>
         </is>
       </c>
-      <c r="B147">
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C147">
         <v>3</v>
       </c>
-      <c r="C147">
+      <c r="D147">
         <v>8.259671939395723E-06</v>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="148">
@@ -3107,16 +3176,16 @@
           <t>SERPINA5</t>
         </is>
       </c>
-      <c r="B148">
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C148">
         <v>2</v>
       </c>
-      <c r="C148">
+      <c r="D148">
         <v>8.027022046721461E-06</v>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="149">
@@ -3125,16 +3194,16 @@
           <t>IGFALS</t>
         </is>
       </c>
-      <c r="B149">
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C149">
         <v>5</v>
       </c>
-      <c r="C149">
+      <c r="D149">
         <v>7.958998711203332E-06</v>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="150">
@@ -3143,16 +3212,16 @@
           <t>IGKV2-30</t>
         </is>
       </c>
-      <c r="B150">
-        <v>1</v>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C150">
+        <v>1</v>
+      </c>
+      <c r="D150">
         <v>7.656113642944973E-06</v>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="151">
@@ -3161,16 +3230,16 @@
           <t>MPO</t>
         </is>
       </c>
-      <c r="B151">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C151">
         <v>6</v>
       </c>
-      <c r="C151">
+      <c r="D151">
         <v>7.463703668897143E-06</v>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="152">
@@ -3179,16 +3248,16 @@
           <t>SERPINA7</t>
         </is>
       </c>
-      <c r="B152">
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C152">
         <v>5</v>
       </c>
-      <c r="C152">
+      <c r="D152">
         <v>7.237197827240801E-06</v>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="153">
@@ -3197,16 +3266,16 @@
           <t>C7</t>
         </is>
       </c>
-      <c r="B153">
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C153">
         <v>13</v>
       </c>
-      <c r="C153">
+      <c r="D153">
         <v>7.027770533529028E-06</v>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="154">
@@ -3215,16 +3284,16 @@
           <t>LPA</t>
         </is>
       </c>
-      <c r="B154">
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C154">
         <v>6</v>
       </c>
-      <c r="C154">
+      <c r="D154">
         <v>6.351008656767059E-06</v>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="155">
@@ -3233,16 +3302,16 @@
           <t>F9</t>
         </is>
       </c>
-      <c r="B155">
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C155">
         <v>7</v>
       </c>
-      <c r="C155">
+      <c r="D155">
         <v>6.204524845667164E-06</v>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="156">
@@ -3251,16 +3320,16 @@
           <t>FETUB</t>
         </is>
       </c>
-      <c r="B156">
-        <v>1</v>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
       </c>
       <c r="C156">
+        <v>1</v>
+      </c>
+      <c r="D156">
         <v>5.66651391548139E-06</v>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="157">
@@ -3269,16 +3338,16 @@
           <t>IGHV3-74</t>
         </is>
       </c>
-      <c r="B157">
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C157">
         <v>2</v>
       </c>
-      <c r="C157">
+      <c r="D157">
         <v>5.097648585131872E-06</v>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="158">
@@ -3287,16 +3356,16 @@
           <t>CPB2</t>
         </is>
       </c>
-      <c r="B158">
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C158">
         <v>5</v>
       </c>
-      <c r="C158">
+      <c r="D158">
         <v>4.909473107248129E-06</v>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="159">
@@ -3305,16 +3374,16 @@
           <t>IGHV3-43</t>
         </is>
       </c>
-      <c r="B159">
-        <v>1</v>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C159">
+        <v>1</v>
+      </c>
+      <c r="D159">
         <v>4.899992335063779E-06</v>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="160">
@@ -3323,16 +3392,16 @@
           <t>PLTP</t>
         </is>
       </c>
-      <c r="B160">
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C160">
         <v>2</v>
       </c>
-      <c r="C160">
+      <c r="D160">
         <v>4.867501129508068E-06</v>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="161">
@@ -3341,16 +3410,16 @@
           <t>ELANE</t>
         </is>
       </c>
-      <c r="B161">
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C161">
         <v>2</v>
       </c>
-      <c r="C161">
+      <c r="D161">
         <v>4.501431092361171E-06</v>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="162">
@@ -3359,16 +3428,16 @@
           <t>IGKV2D-29</t>
         </is>
       </c>
-      <c r="B162">
-        <v>1</v>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C162">
+        <v>1</v>
+      </c>
+      <c r="D162">
         <v>4.430895987008919E-06</v>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="163">
@@ -3377,16 +3446,16 @@
           <t>GP1BA</t>
         </is>
       </c>
-      <c r="B163">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C163">
         <v>2</v>
       </c>
-      <c r="C163">
+      <c r="D163">
         <v>4.317437843630169E-06</v>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="164">
@@ -3395,16 +3464,16 @@
           <t>HBM</t>
         </is>
       </c>
-      <c r="B164">
-        <v>1</v>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C164">
+        <v>1</v>
+      </c>
+      <c r="D164">
         <v>4.088188966787161E-06</v>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="165">
@@ -3413,16 +3482,16 @@
           <t>IGHV1-69</t>
         </is>
       </c>
-      <c r="B165">
-        <v>1</v>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C165">
+        <v>1</v>
+      </c>
+      <c r="D165">
         <v>4.043897195599924E-06</v>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="166">
@@ -3431,16 +3500,16 @@
           <t>C1RL</t>
         </is>
       </c>
-      <c r="B166">
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C166">
         <v>3</v>
       </c>
-      <c r="C166">
+      <c r="D166">
         <v>3.32952414238425E-06</v>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="167">
@@ -3449,16 +3518,16 @@
           <t>IGLV2-11</t>
         </is>
       </c>
-      <c r="B167">
-        <v>1</v>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C167">
+        <v>1</v>
+      </c>
+      <c r="D167">
         <v>3.181095917114398E-06</v>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="168">
@@ -3467,16 +3536,16 @@
           <t>IGHV1-2</t>
         </is>
       </c>
-      <c r="B168">
-        <v>1</v>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C168">
+        <v>1</v>
+      </c>
+      <c r="D168">
         <v>3.16496312122162E-06</v>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="169">
@@ -3485,16 +3554,16 @@
           <t>CSTA</t>
         </is>
       </c>
-      <c r="B169">
-        <v>1</v>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
       </c>
       <c r="C169">
+        <v>1</v>
+      </c>
+      <c r="D169">
         <v>2.590751926177666E-06</v>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="170">
@@ -3503,16 +3572,16 @@
           <t>IGHV1-18</t>
         </is>
       </c>
-      <c r="B170">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C170">
         <v>2</v>
       </c>
-      <c r="C170">
+      <c r="D170">
         <v>2.46637811965505E-06</v>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="171">
@@ -3521,16 +3590,16 @@
           <t>IGLV6-57</t>
         </is>
       </c>
-      <c r="B171">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C171">
         <v>2</v>
       </c>
-      <c r="C171">
+      <c r="D171">
         <v>2.195727021246762E-06</v>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="172">
@@ -3539,16 +3608,16 @@
           <t>IGLV3-9</t>
         </is>
       </c>
-      <c r="B172">
-        <v>1</v>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C172">
+        <v>1</v>
+      </c>
+      <c r="D172">
         <v>2.165543635678785E-06</v>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="173">
@@ -3557,16 +3626,16 @@
           <t>LCAT</t>
         </is>
       </c>
-      <c r="B173">
-        <v>1</v>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
       </c>
       <c r="C173">
+        <v>1</v>
+      </c>
+      <c r="D173">
         <v>2.163801211812924E-06</v>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="174">
@@ -3575,16 +3644,16 @@
           <t>IGLV8-61</t>
         </is>
       </c>
-      <c r="B174">
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C174">
         <v>2</v>
       </c>
-      <c r="C174">
+      <c r="D174">
         <v>1.717867420362343E-06</v>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="175">
@@ -3593,16 +3662,16 @@
           <t>F13B</t>
         </is>
       </c>
-      <c r="B175">
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C175">
         <v>5</v>
       </c>
-      <c r="C175">
+      <c r="D175">
         <v>1.646724886278185E-06</v>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="176">
@@ -3611,16 +3680,16 @@
           <t>GPLD1</t>
         </is>
       </c>
-      <c r="B176">
-        <v>1</v>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
       </c>
       <c r="C176">
+        <v>1</v>
+      </c>
+      <c r="D176">
         <v>1.547354078698953E-06</v>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="177">
@@ -3629,16 +3698,16 @@
           <t>HABP2</t>
         </is>
       </c>
-      <c r="B177">
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C177">
         <v>2</v>
       </c>
-      <c r="C177">
+      <c r="D177">
         <v>1.46030305056862E-06</v>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="178">
@@ -3647,16 +3716,16 @@
           <t>APOF</t>
         </is>
       </c>
-      <c r="B178">
-        <v>1</v>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
       </c>
       <c r="C178">
+        <v>1</v>
+      </c>
+      <c r="D178">
         <v>1.450363058221785E-06</v>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="179">
@@ -3665,16 +3734,16 @@
           <t>SBSN</t>
         </is>
       </c>
-      <c r="B179">
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C179">
         <v>4</v>
       </c>
-      <c r="C179">
+      <c r="D179">
         <v>1.423445299800372E-06</v>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="180">
@@ -3683,16 +3752,16 @@
           <t>LBP</t>
         </is>
       </c>
-      <c r="B180">
-        <v>1</v>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
       </c>
       <c r="C180">
+        <v>1</v>
+      </c>
+      <c r="D180">
         <v>1.355279028935263E-06</v>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="181">
@@ -3701,16 +3770,16 @@
           <t>BTD</t>
         </is>
       </c>
-      <c r="B181">
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C181">
         <v>4</v>
       </c>
-      <c r="C181">
+      <c r="D181">
         <v>1.343428229424486E-06</v>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="182">
@@ -3719,16 +3788,16 @@
           <t>IGLV3-10</t>
         </is>
       </c>
-      <c r="B182">
-        <v>1</v>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C182">
+        <v>1</v>
+      </c>
+      <c r="D182">
         <v>1.314287781861307E-06</v>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="183">
@@ -3737,16 +3806,16 @@
           <t>CPN1</t>
         </is>
       </c>
-      <c r="B183">
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C183">
         <v>2</v>
       </c>
-      <c r="C183">
+      <c r="D183">
         <v>1.177680911055654E-06</v>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="184">
@@ -3755,16 +3824,16 @@
           <t>KRT13</t>
         </is>
       </c>
-      <c r="B184">
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C184">
         <v>2</v>
       </c>
-      <c r="C184">
+      <c r="D184">
         <v>1.115509622237393E-06</v>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="185">
@@ -3773,16 +3842,16 @@
           <t>SELENOP</t>
         </is>
       </c>
-      <c r="B185">
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C185">
         <v>2</v>
       </c>
-      <c r="C185">
+      <c r="D185">
         <v>1.049479511461922E-06</v>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="186">
@@ -3791,16 +3860,16 @@
           <t>MASP1</t>
         </is>
       </c>
-      <c r="B186">
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C186">
         <v>2</v>
       </c>
-      <c r="C186">
+      <c r="D186">
         <v>9.548272372276714E-07</v>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="187">
@@ -3809,16 +3878,16 @@
           <t>KRT5</t>
         </is>
       </c>
-      <c r="B187">
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C187">
         <v>2</v>
       </c>
-      <c r="C187">
+      <c r="D187">
         <v>9.409707925566078E-07</v>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="188">
@@ -3827,16 +3896,16 @@
           <t>IGLC7</t>
         </is>
       </c>
-      <c r="B188">
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C188">
         <v>2</v>
       </c>
-      <c r="C188">
+      <c r="D188">
         <v>9.18860461103716E-07</v>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="189">
@@ -3845,16 +3914,16 @@
           <t>IGLV4-69</t>
         </is>
       </c>
-      <c r="B189">
-        <v>1</v>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C189">
+        <v>1</v>
+      </c>
+      <c r="D189">
         <v>8.492540692692635E-07</v>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="190">
@@ -3863,16 +3932,16 @@
           <t>F12</t>
         </is>
       </c>
-      <c r="B190">
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C190">
         <v>3</v>
       </c>
-      <c r="C190">
+      <c r="D190">
         <v>8.170241716732337E-07</v>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="191">
@@ -3881,16 +3950,16 @@
           <t>C4BPB</t>
         </is>
       </c>
-      <c r="B191">
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C191">
         <v>2</v>
       </c>
-      <c r="C191">
+      <c r="D191">
         <v>7.982071060406515E-07</v>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="192">
@@ -3899,16 +3968,16 @@
           <t>IGKV1-16</t>
         </is>
       </c>
-      <c r="B192">
-        <v>1</v>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C192">
+        <v>1</v>
+      </c>
+      <c r="D192">
         <v>7.914664083371467E-07</v>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="193">
@@ -3917,16 +3986,16 @@
           <t>HRNR</t>
         </is>
       </c>
-      <c r="B193">
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C193">
         <v>7</v>
       </c>
-      <c r="C193">
+      <c r="D193">
         <v>7.408035176441298E-07</v>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="194">
@@ -3935,16 +4004,16 @@
           <t>RNASE3</t>
         </is>
       </c>
-      <c r="B194">
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C194">
         <v>2</v>
       </c>
-      <c r="C194">
+      <c r="D194">
         <v>7.185869088676039E-07</v>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="195">
@@ -3953,16 +4022,16 @@
           <t>CFHR2</t>
         </is>
       </c>
-      <c r="B195">
-        <v>1</v>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
       </c>
       <c r="C195">
+        <v>1</v>
+      </c>
+      <c r="D195">
         <v>7.006030397622389E-07</v>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="196">
@@ -3971,16 +4040,16 @@
           <t>F10</t>
         </is>
       </c>
-      <c r="B196">
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C196">
         <v>2</v>
       </c>
-      <c r="C196">
+      <c r="D196">
         <v>6.449498446430174E-07</v>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="197">
@@ -3989,16 +4058,16 @@
           <t>F11</t>
         </is>
       </c>
-      <c r="B197">
-        <v>1</v>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
       </c>
       <c r="C197">
+        <v>1</v>
+      </c>
+      <c r="D197">
         <v>6.296928049958023E-07</v>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="198">
@@ -4007,16 +4076,16 @@
           <t>GMFG</t>
         </is>
       </c>
-      <c r="B198">
-        <v>1</v>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
       </c>
       <c r="C198">
+        <v>1</v>
+      </c>
+      <c r="D198">
         <v>5.749332455907179E-07</v>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="199">
@@ -4025,16 +4094,16 @@
           <t>PRTN3</t>
         </is>
       </c>
-      <c r="B199">
-        <v>1</v>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
       </c>
       <c r="C199">
+        <v>1</v>
+      </c>
+      <c r="D199">
         <v>4.387743341396962E-07</v>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="200">
@@ -4043,16 +4112,16 @@
           <t>SAA1</t>
         </is>
       </c>
-      <c r="B200">
-        <v>1</v>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
       </c>
       <c r="C200">
+        <v>1</v>
+      </c>
+      <c r="D200">
         <v>2.765082233746705E-07</v>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="201">
@@ -4061,16 +4130,16 @@
           <t>SPRR2G</t>
         </is>
       </c>
-      <c r="B201">
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C201">
         <v>2</v>
       </c>
-      <c r="C201">
+      <c r="D201">
         <v>2.591212742069314E-07</v>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="202">
@@ -4079,16 +4148,16 @@
           <t>GIMAP1</t>
         </is>
       </c>
-      <c r="B202">
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="C202">
         <v>3</v>
       </c>
-      <c r="C202">
+      <c r="D202">
         <v>2.44627700189718E-07</v>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="203">
@@ -4097,16 +4166,16 @@
           <t>KRT16</t>
         </is>
       </c>
-      <c r="B203">
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C203">
         <v>2</v>
       </c>
-      <c r="C203">
+      <c r="D203">
         <v>2.071701442218259E-07</v>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="204">
@@ -4115,16 +4184,16 @@
           <t>KEL</t>
         </is>
       </c>
-      <c r="B204">
-        <v>1</v>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
       </c>
       <c r="C204">
+        <v>1</v>
+      </c>
+      <c r="D204">
         <v>1.281596724669341E-07</v>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="205">
@@ -4133,16 +4202,16 @@
           <t>KRTAP3-1</t>
         </is>
       </c>
-      <c r="B205">
-        <v>1</v>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C205">
+        <v>1</v>
+      </c>
+      <c r="D205">
         <v>1.063139419745648E-07</v>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="206">
@@ -4151,16 +4220,16 @@
           <t>GIMAP4</t>
         </is>
       </c>
-      <c r="B206">
-        <v>1</v>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
       </c>
       <c r="C206">
+        <v>1</v>
+      </c>
+      <c r="D206">
         <v>1.040228525418127E-07</v>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="207">
@@ -4169,16 +4238,16 @@
           <t>SHBG</t>
         </is>
       </c>
-      <c r="B207">
-        <v>1</v>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
       </c>
       <c r="C207">
+        <v>1</v>
+      </c>
+      <c r="D207">
         <v>1.013353822162655E-07</v>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="208">
@@ -4187,16 +4256,16 @@
           <t>FYB1</t>
         </is>
       </c>
-      <c r="B208">
-        <v>1</v>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
       </c>
       <c r="C208">
+        <v>1</v>
+      </c>
+      <c r="D208">
         <v>7.935662162075505E-08</v>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="209">
@@ -4205,16 +4274,16 @@
           <t>KRT14</t>
         </is>
       </c>
-      <c r="B209">
-        <v>1</v>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C209">
+        <v>1</v>
+      </c>
+      <c r="D209">
         <v>7.777506077462222E-08</v>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="210">
@@ -4223,16 +4292,16 @@
           <t>IGHV2-5</t>
         </is>
       </c>
-      <c r="B210">
-        <v>1</v>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C210">
+        <v>1</v>
+      </c>
+      <c r="D210">
         <v>6.903848909574007E-08</v>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
     <row r="211">
@@ -4241,16 +4310,16 @@
           <t>CFHR5</t>
         </is>
       </c>
-      <c r="B211">
-        <v>1</v>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
       </c>
       <c r="C211">
+        <v>1</v>
+      </c>
+      <c r="D211">
         <v>3.867351756390219E-08</v>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
       </c>
     </row>
     <row r="212">
@@ -4259,16 +4328,16 @@
           <t>IGLV2-23</t>
         </is>
       </c>
-      <c r="B212">
-        <v>1</v>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
       </c>
       <c r="C212">
+        <v>1</v>
+      </c>
+      <c r="D212">
         <v>3.635119439611477E-08</v>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/01_Preprocess/01_Filtering/c_data/01_filter.xlsx
+++ b/01_Preprocess/01_Filtering/c_data/01_filter.xlsx
@@ -392,7 +392,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Precursors, protein groups and share of starting signal after each filter</t>
+          <t>Rows, groups and signal after each filter</t>
         </is>
       </c>
     </row>
@@ -410,7 +410,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Contaminant symbol strings removed, how each matched, and the signal it carried</t>
+          <t>Removed contaminants and their signal</t>
         </is>
       </c>
     </row>

--- a/01_Preprocess/01_Filtering/c_data/01_filter.xlsx
+++ b/01_Preprocess/01_Filtering/c_data/01_filter.xlsx
@@ -8,8 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="overview" sheetId="1" r:id="rId1"/>
-    <sheet name="filter_log" sheetId="2" r:id="rId2"/>
-    <sheet name="contaminants_removed" sheetId="3" r:id="rId3"/>
+    <sheet name="samples" sheetId="2" r:id="rId2"/>
+    <sheet name="filtering_summary" sheetId="3" r:id="rId3"/>
+    <sheet name="annotation_exclusions" sheetId="4" r:id="rId4"/>
+    <sheet name="removed_contaminants" sheetId="5" r:id="rId5"/>
+    <sheet name="sample_contamination" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -353,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,36 +384,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>filter_log</t>
+          <t>samples</t>
         </is>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>131</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rows, groups and signal after each filter</t>
+          <t>Sample identifiers and study metadata</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>contaminants_removed</t>
+          <t>filtering_summary</t>
         </is>
       </c>
       <c r="B3">
-        <v>211</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Removed contaminants and their signal</t>
+          <t>Rows, groups and percentage of original starting signal retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>annotation_exclusions</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Overlapping annotation categories; percentages use original starting signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>removed_contaminants</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>211</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Excluded gene-symbol entries and percentage of original starting signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sample_contamination</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>131</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Per-sample percentage removed, relative to signal just before contaminant filtering</t>
         </is>
       </c>
     </row>
@@ -421,93 +478,5551 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>sample_id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>precursors</t>
+          <t>participant</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>protein_groups</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>pct_signal</t>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>timepoint</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>sex</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>repaired</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>53760</v>
-      </c>
-      <c r="C2">
-        <v>3736</v>
-      </c>
-      <c r="D2">
-        <v>99.72765070997796</v>
+          <t>S02_L_T1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CL_MDR_2E-T1</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>shared peptides removed</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>49801</v>
-      </c>
-      <c r="C3">
-        <v>3664</v>
-      </c>
-      <c r="D3">
-        <v>85.94764178778486</v>
+          <t>S02_L_T2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CL_MDR_2E-T2</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>compound groups removed</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>49788</v>
-      </c>
-      <c r="C4">
-        <v>3662</v>
-      </c>
-      <c r="D4">
-        <v>85.94736147006761</v>
+          <t>S02_R_T1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CL_MR_2D_T1</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>contaminants removed</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>47133</v>
-      </c>
-      <c r="C5">
-        <v>3451</v>
-      </c>
-      <c r="D5">
-        <v>57.99577454956071</v>
+          <t>S02_R_T2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CL_MR_2D_T2r</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S03_L_T1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CL_MDR_3E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S03_L_T2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CL_MDR_3E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S03_R_T1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CL_MDR_3D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>S03_R_T2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>CL_MDR_3D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S04_L_T1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CL_MDR_4E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S04_L_T2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CL_MDR_4E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S04_R_T1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>CL_MDR_4D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S04_R_T2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>CL_MDR_4D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S05_L_T1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>CL_MDR_5E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>S05_L_T2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>CL_MDR_5E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S05_R_T1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>CL_MDR_5D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S05_R_T2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>CL_MDR_5D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S06_L_T1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>CL_MDR_6E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S06_R_T1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>CL_MR_6D_T1r</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S06_R_T2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>CL_MR_6D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S07_L_T1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>CL_MR_7E_T1r</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S07_L_T2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>CL_MDR_7E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>S07_R_T1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CL_MDR_7D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>S07_R_T2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>CL_MDR_7D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>S08_L_T1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>CL_MDR_8E-T1r</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>S08_L_T2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>CL_MDR_8E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>S08_R_T1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>CL_MDR_8D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>S08_R_T2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>CL_MR_8D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S09_L_T1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>CL_MDR_9E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S09_L_T2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>CL_MDR_9E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>S09_R_T1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>CL_MDR_9D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>S09_R_T2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>CL_MDR_9D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>S10_L_T1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>CL_MDR_10E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>S10_L_T2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>CL_MDR_10E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>S10_R_T1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>CL_MDR_10D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>S10_R_T2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>CL_MDR_10D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>S11_L_T1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>CL_MDR_11E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>S11_L_T2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>CL_MDR_11E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>S11_R_T1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>CL_MDR_11D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>S11_R_T2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>CL_MDR_11D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>S12_L_T1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>CL_MDR_12E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>S12_L_T2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>CL_MDR_12E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>S12_R_T1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>CL_MDR_12D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>S12_R_T2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>CL_MDR_12D-T2rR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>S13_L_T1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>CL_MDR_13E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>S13_L_T2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>CL_MDR_13E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>S13_R_T1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>CL_MDR_13D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>S13_R_T2</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>CL_MDR_13D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>S14_L_T1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>CL_MDR_14E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>S14_L_T2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>CL_MDR_14E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>S14_R_T1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>CL_MDR_14D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>S14_R_T2</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>CL_MDR_14D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>S15_L_T1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>CL_MDR_15E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>S15_L_T2</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>CL_MDR_15E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>S15_R_T1</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>CL_MDR_15D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>S15_R_T2</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>CL_MDR_15D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>S16_L_T1</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>CL_MR_16E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>S16_L_T2</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>CL_MR_16E_T2r</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>S16_R_T1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>CL_MDR_16D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>S16_R_T2</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>CL_MDR_16D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>S17_L_T1</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>CL_MDR_17E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S17_L_T2</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>CL_MDR_17E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>S17_R_T1</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>CL_MDR_17D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>S17_R_T2</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>CL_MDR_17D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>S18_L_T1</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>S18</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>CL_MDR_18E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>S18_L_T2</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>S18</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>CL_MDR_18E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>S18_R_T1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>S18</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>CL_MDR_18D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>S18_R_T2</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>S18</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>CL_MDR_18D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>S20_L_T1</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>CL_MDR_20E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>S20_L_T2</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>CL_MDR_20E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>S20_R_T1</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>CL_MDR_20D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>S20_R_T2</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>CL_MDR_20D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>S21_L_T1</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>S21</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>CL_MDR_21E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>S21_L_T2</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>S21</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>CL_MDR_21E_T2r</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>S21_R_T1</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>S21</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>CL_MDR_21D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>S21_R_T2</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>S21</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>CL_MDR_21D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>S23_L_T1</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>S23</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>CL_MDR_23E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>S23_L_T2</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>S23</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>CL_MDR_23E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>S23_R_T1</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>S23</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>CL_MDR_23D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>S23_R_T2</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>S23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>CL_MDR_23D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>S24_L_T1</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>S24</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>CL_MDR_24E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>S24_L_T2</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>S24</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>CL_MDR_24E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>S24_R_T1</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>S24</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>CL_MDR_24D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>S24_R_T2</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>S24</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>CL_MDR_24D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>S25_L_T1</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>CL_MDR_25E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>S25_L_T2</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>CL_MDR_25E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>S25_R_T1</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>CL_MDR_25D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>S25_R_T2</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>CL_MDR_25D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>S26_L_T1</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>S26</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>CL_MDR_26E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>S26_L_T2</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>S26</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>CL_MDR_26E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>S26_R_T1</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>S26</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>CL_MDR_26D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>S26_R_T2</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>S26</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>CL_MDR_26D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>S27_L_T1</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>S27</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>CL_MDR_27E_T1r</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>S27_L_T2</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>S27</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>CL_MDR_27E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>S27_R_T1</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>S27</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>CL_MDR_27D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>S27_R_T2</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>S27</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>CL_MDR_27D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>S28_L_T1</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>S28</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>CL_MDR_28E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>S28_L_T2</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>S28</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>CL_MDR_28E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>S28_R_T1</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>S28</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>CL_MDR_28D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>S28_R_T2</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>S28</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>CL_MDR_28D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>S29_L_T1</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>CL_MDR_29E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>S29_L_T2</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>CL_MDR_29E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>S29_R_T1</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>CL_MDR_29D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>S29_R_T2</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>CL_MDR_29D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>S30_L_T1</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>S30</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>CL_MDR_30E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>S30_L_T2</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>S30</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>CL_MDR_30E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>S30_R_T1</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>S30</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>CL_MDR_30D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>S30_R_T2</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>S30</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>CL_MDR_30D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>S31_L_T1</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>S31</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>CL_MDR_31E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>S31_L_T2</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>S31</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>CL_MDR_31E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>S31_R_T1</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>S31</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>CL_MDR_31D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>S31_R_T2</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>S31</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>CL_MDR_31D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>S32_L_T1</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>CL_MDR_32E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>S32_L_T2</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>CL_MDR_32E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>S32_R_T1</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>CL_MDR_32D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>S32_R_T2</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>CL_MDR_32D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>S33_L_T1</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>S33</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>CL_MDR_33E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>S33_L_T2</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>S33</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>CL_MDR_33E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>S33_R_T1</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>S33</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>CL_MDR_33D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>S33_R_T2</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>S33</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>CL_MDR_33D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>S35_L_T1</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>S35</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>CL_MDR_35E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>S35_L_T2</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>S35</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>CL_MDR_35E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>S35_R_T1</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>S35</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>CL_MDR_35D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>S35_R_T2</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>S35</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>CL_MDR_35D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>S36_L_T1</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>S36</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>CL_MDR_36E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>S36_L_T2</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>S36</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>CL_MDR_36E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>S36_R_T1</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>S36</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>CL_MDR_36D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>S36_R_T2</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>S36</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>CL_MDR_36D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>S37_L_T1</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>S37</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>CL_MDR_37E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>S37_L_T2</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>S37</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>CL_MDR_37E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>S37_R_T1</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>S37</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>CL_MDR_37D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>S37_R_T2</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>S37</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>CL_MDR_37D-T2</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -517,6 +6032,168 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>precursors</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>protein_groups</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>pct_signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>repaired</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>53760</v>
+      </c>
+      <c r="C2">
+        <v>3736</v>
+      </c>
+      <c r="D2">
+        <v>99.72765070997796</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>shared peptides removed</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>49801</v>
+      </c>
+      <c r="C3">
+        <v>3664</v>
+      </c>
+      <c r="D3">
+        <v>85.94764178778486</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>compound groups removed</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>49788</v>
+      </c>
+      <c r="C4">
+        <v>3662</v>
+      </c>
+      <c r="D4">
+        <v>85.94736147006761</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>contaminants removed</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>47133</v>
+      </c>
+      <c r="C5">
+        <v>3451</v>
+      </c>
+      <c r="D5">
+        <v>57.99577454956071</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>precursors</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>pct_signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>cRAP-only group</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>73</v>
+      </c>
+      <c r="C2">
+        <v>0.2712919611357874</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>reversed decoy</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>19</v>
+      </c>
+      <c r="C3">
+        <v>0.001057328886625115</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mentions cRAP at all</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>1258</v>
+      </c>
+      <c r="C4">
+        <v>64.79051964118159</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D212"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -4343,4 +10020,1996 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C132"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>sample_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>pct_signal_removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>S02_L_T1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>47.67588762314584</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>S02_L_T2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>32.94531359061347</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>S02_R_T1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>26.92237039484356</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>S02_R_T2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>44.22737005130872</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S03_L_T1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>32.84756828876942</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S03_L_T2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>33.77546156372504</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S03_R_T1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>26.30610564617677</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>S03_R_T2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>30.12823711674234</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S04_L_T1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>23.28056718797209</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S04_L_T2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>23.85657703181791</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S04_R_T1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>80.04730964967737</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S04_R_T2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>47.56105652460237</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S05_L_T1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>43.69280840733837</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>S05_L_T2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>21.18864330904015</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S05_R_T1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>22.75198845249871</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S05_R_T2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>42.15387739667176</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S06_L_T1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>23.54008820945759</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S06_R_T1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>29.38593188164029</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S06_R_T2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>22.46195728590685</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S07_L_T1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>20.35367056542408</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S07_L_T2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>27.96902476406055</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>S07_R_T1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>21.17139491633812</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>S07_R_T2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>23.87527495594478</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>S08_L_T1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>32.69182469649088</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>S08_L_T2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>30.93423891106747</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>S08_R_T1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>28.42310620817203</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>S08_R_T2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>16.63941848888081</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S09_L_T1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>42.30503174963643</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S09_L_T2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>34.37055072267925</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>S09_R_T1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>38.36347537032253</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>S09_R_T2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>47.64520736723398</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>S10_L_T1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>30.66402268078223</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>S10_L_T2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>39.74600589103538</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>S10_R_T1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>28.86995422984455</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>S10_R_T2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>28.14711412007461</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>S11_L_T1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>39.66854222119643</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>S11_L_T2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>45.34839915363387</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>S11_R_T1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>27.00680589104332</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>S11_R_T2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>41.67922369256501</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>S12_L_T1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>21.71493658086321</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>S12_L_T2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>48.19129352447257</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>S12_R_T1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>31.81801040014127</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>S12_R_T2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>41.90130733169551</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>S13_L_T1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>31.53510281837602</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>S13_L_T2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>38.16586452970394</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>S13_R_T1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>27.94183611072752</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>S13_R_T2</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>36.60418227648745</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>S14_L_T1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>35.59251471492991</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>S14_L_T2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>39.43944411093926</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>S14_R_T1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>19.83335642665108</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>S14_R_T2</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>30.26778016834878</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>S15_L_T1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>26.76418571869921</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>S15_L_T2</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>21.70452816943379</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>S15_R_T1</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>26.78763204874603</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>S15_R_T2</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>14.61785164370152</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>S16_L_T1</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>46.26017565198951</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>S16_L_T2</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>33.30886079618666</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>S16_R_T1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>56.12512896531096</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>S16_R_T2</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>44.93578198376525</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>S17_L_T1</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>36.62097245644279</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S17_L_T2</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>29.93956069031647</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>S17_R_T1</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>15.94567341877486</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>S17_R_T2</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>35.80492528665793</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>S18_L_T1</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>22.7417335321488</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>S18_L_T2</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>16.8602152144968</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>S18_R_T1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>35.99984187396467</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>S18_R_T2</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>16.69561257390728</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>S20_L_T1</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>23.20450141981969</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>S20_L_T2</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>20.57305290455586</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>S20_R_T1</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>34.79292282301629</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>S20_R_T2</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>34.06564329310944</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>S21_L_T1</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>10.96343246605272</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>S21_L_T2</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>7.969572023574983</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>S21_R_T1</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>16.74537085623831</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>S21_R_T2</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>29.87067839546477</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>S23_L_T1</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>16.91498872609365</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>S23_L_T2</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>39.54245235445715</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>S23_R_T1</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>24.60595487784461</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>S23_R_T2</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>28.91965199581156</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>S24_L_T1</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>21.61977225324352</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>S24_L_T2</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>30.38060629001883</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>S24_R_T1</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>12.70941514144465</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>S24_R_T2</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>41.06654871542835</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>S25_L_T1</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>36.99648992657553</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>S25_L_T2</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>24.45009777568204</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>S25_R_T1</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>24.71441180559659</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>S25_R_T2</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>52.97662653530515</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>S26_L_T1</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>38.96394370949655</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>S26_L_T2</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>23.84487039831377</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>S26_R_T1</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>26.03918565573812</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>S26_R_T2</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>25.36370339452061</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>S27_L_T1</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>15.37613566725733</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>S27_L_T2</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>29.66137073655472</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>S27_R_T1</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>21.10797206848373</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>S27_R_T2</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>12.31488381482708</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>S28_L_T1</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>26.06550270766389</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>S28_L_T2</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>21.86709376479077</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>S28_R_T1</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>56.91174655003424</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>S28_R_T2</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>19.4494897405777</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>S29_L_T1</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>25.7404046871725</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>S29_L_T2</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>39.20822070311088</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>S29_R_T1</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>23.22997484491086</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>S29_R_T2</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>21.00803406083094</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>S30_L_T1</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>20.77715452642849</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>S30_L_T2</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>39.97566362823648</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>S30_R_T1</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>25.2190042862803</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>S30_R_T2</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>29.09747088402708</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>S31_L_T1</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>12.76292426989062</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>S31_L_T2</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>27.88902870682065</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>S31_R_T1</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>25.46757510230898</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>S31_R_T2</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>11.80556463739358</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>S32_L_T1</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>39.3487605731198</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>S32_L_T2</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>18.15335844244948</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>S32_R_T1</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>34.02997538438925</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>S32_R_T2</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>32.71684271846188</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>S33_L_T1</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>36.42309241970267</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>S33_L_T2</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>7.030525483221525</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>S33_R_T1</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>18.83582962865379</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>S33_R_T2</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>20.84774351157882</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>S35_L_T1</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>20.64031541564402</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>S35_L_T2</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>47.02820160443556</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>S35_R_T1</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>27.16603170315223</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>S35_R_T2</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>32.2471799147256</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>S36_L_T1</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>23.18245701507416</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>S36_L_T2</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>21.29972454452716</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>S36_R_T1</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>36.83350895420893</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>S36_R_T2</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>16.40526740598066</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>S37_L_T1</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>40.84166261694882</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>S37_L_T2</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>30.97555630635593</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>S37_R_T1</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>33.04784603373193</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>S37_R_T2</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>49.3457184924102</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/01_Preprocess/01_Filtering/c_data/01_filter.xlsx
+++ b/01_Preprocess/01_Filtering/c_data/01_filter.xlsx
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>53760</v>
+        <v>53744</v>
       </c>
       <c r="C2">
-        <v>3736</v>
+        <v>3734</v>
       </c>
       <c r="D2">
-        <v>99.72765070997796</v>
+        <v>98.58844075613163</v>
       </c>
     </row>
     <row r="3">
@@ -5957,13 +5957,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>49801</v>
+        <v>49871</v>
       </c>
       <c r="C3">
         <v>3664</v>
       </c>
       <c r="D3">
-        <v>85.94764178778486</v>
+        <v>87.63098062339989</v>
       </c>
     </row>
     <row r="4">
@@ -5973,13 +5973,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>49788</v>
+        <v>49858</v>
       </c>
       <c r="C4">
         <v>3662</v>
       </c>
       <c r="D4">
-        <v>85.94736147006761</v>
+        <v>87.63070030568271</v>
       </c>
     </row>
     <row r="5">
@@ -5989,13 +5989,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>47133</v>
+        <v>47201</v>
       </c>
       <c r="C5">
         <v>3451</v>
       </c>
       <c r="D5">
-        <v>57.99577454956071</v>
+        <v>59.67866240498889</v>
       </c>
     </row>
   </sheetData>
@@ -6032,10 +6032,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C2">
-        <v>0.2712919611357874</v>
+        <v>1.410501914983034</v>
       </c>
     </row>
     <row r="3">
@@ -6486,10 +6486,10 @@
         </is>
       </c>
       <c r="C23">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D23">
-        <v>0.006134026491755945</v>
+        <v>0.006253658895711615</v>
       </c>
     </row>
     <row r="24">
@@ -6711,7 +6711,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IGHG3</t>
+          <t>KRT10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6720,46 +6720,46 @@
         </is>
       </c>
       <c r="C36">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D36">
-        <v>0.002033071723152557</v>
+        <v>0.002113686068996637</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>APOH</t>
+          <t>IGHG3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C37">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D37">
-        <v>0.001834766275260182</v>
+        <v>0.002033071723152557</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KRT10</t>
+          <t>APOH</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="C38">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D38">
-        <v>0.001782338284746402</v>
+        <v>0.001834766275260182</v>
       </c>
     </row>
     <row r="39">
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>47.67588762314584</v>
+        <v>47.02304114647254</v>
       </c>
     </row>
     <row r="3">
@@ -9948,7 +9948,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>32.94531359061347</v>
+        <v>32.55712075226026</v>
       </c>
     </row>
     <row r="4">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>26.92237039484356</v>
+        <v>26.36469023306657</v>
       </c>
     </row>
     <row r="5">
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>44.22737005130872</v>
+        <v>43.53350247764178</v>
       </c>
     </row>
     <row r="6">
@@ -9993,7 +9993,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>32.84756828876942</v>
+        <v>32.39487348948416</v>
       </c>
     </row>
     <row r="7">
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>33.77546156372504</v>
+        <v>33.31482870417345</v>
       </c>
     </row>
     <row r="8">
@@ -10023,7 +10023,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>26.30610564617677</v>
+        <v>25.91978552525977</v>
       </c>
     </row>
     <row r="9">
@@ -10038,7 +10038,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>30.12823711674234</v>
+        <v>29.72067622593642</v>
       </c>
     </row>
     <row r="10">
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="C10">
-        <v>23.28056718797209</v>
+        <v>23.00692063974904</v>
       </c>
     </row>
     <row r="11">
@@ -10068,7 +10068,7 @@
         </is>
       </c>
       <c r="C11">
-        <v>23.85657703181791</v>
+        <v>23.33137910666068</v>
       </c>
     </row>
     <row r="12">
@@ -10083,7 +10083,7 @@
         </is>
       </c>
       <c r="C12">
-        <v>80.04730964967737</v>
+        <v>79.41277992510496</v>
       </c>
     </row>
     <row r="13">
@@ -10098,7 +10098,7 @@
         </is>
       </c>
       <c r="C13">
-        <v>47.56105652460237</v>
+        <v>47.01711075034413</v>
       </c>
     </row>
     <row r="14">
@@ -10113,7 +10113,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>43.69280840733837</v>
+        <v>43.16364657622505</v>
       </c>
     </row>
     <row r="15">
@@ -10128,7 +10128,7 @@
         </is>
       </c>
       <c r="C15">
-        <v>21.18864330904015</v>
+        <v>20.78960794558883</v>
       </c>
     </row>
     <row r="16">
@@ -10143,7 +10143,7 @@
         </is>
       </c>
       <c r="C16">
-        <v>22.75198845249871</v>
+        <v>22.41970779267011</v>
       </c>
     </row>
     <row r="17">
@@ -10158,7 +10158,7 @@
         </is>
       </c>
       <c r="C17">
-        <v>42.15387739667176</v>
+        <v>41.51855872401673</v>
       </c>
     </row>
     <row r="18">
@@ -10173,7 +10173,7 @@
         </is>
       </c>
       <c r="C18">
-        <v>23.54008820945759</v>
+        <v>23.12442177215729</v>
       </c>
     </row>
     <row r="19">
@@ -10188,7 +10188,7 @@
         </is>
       </c>
       <c r="C19">
-        <v>29.38593188164029</v>
+        <v>28.8023231470601</v>
       </c>
     </row>
     <row r="20">
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="C20">
-        <v>22.46195728590685</v>
+        <v>21.81614435383804</v>
       </c>
     </row>
     <row r="21">
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="C21">
-        <v>20.35367056542408</v>
+        <v>19.76410868241904</v>
       </c>
     </row>
     <row r="22">
@@ -10233,7 +10233,7 @@
         </is>
       </c>
       <c r="C22">
-        <v>27.96902476406055</v>
+        <v>27.665080911571</v>
       </c>
     </row>
     <row r="23">
@@ -10248,7 +10248,7 @@
         </is>
       </c>
       <c r="C23">
-        <v>21.17139491633812</v>
+        <v>20.74119469340042</v>
       </c>
     </row>
     <row r="24">
@@ -10263,7 +10263,7 @@
         </is>
       </c>
       <c r="C24">
-        <v>23.87527495594478</v>
+        <v>23.44822584218077</v>
       </c>
     </row>
     <row r="25">
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="C25">
-        <v>32.69182469649088</v>
+        <v>32.33712726566275</v>
       </c>
     </row>
     <row r="26">
@@ -10293,7 +10293,7 @@
         </is>
       </c>
       <c r="C26">
-        <v>30.93423891106747</v>
+        <v>30.61677370438202</v>
       </c>
     </row>
     <row r="27">
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="C27">
-        <v>28.42310620817203</v>
+        <v>27.94241417164917</v>
       </c>
     </row>
     <row r="28">
@@ -10323,7 +10323,7 @@
         </is>
       </c>
       <c r="C28">
-        <v>16.63941848888081</v>
+        <v>16.1899190370299</v>
       </c>
     </row>
     <row r="29">
@@ -10338,7 +10338,7 @@
         </is>
       </c>
       <c r="C29">
-        <v>42.30503174963643</v>
+        <v>41.79544804452135</v>
       </c>
     </row>
     <row r="30">
@@ -10353,7 +10353,7 @@
         </is>
       </c>
       <c r="C30">
-        <v>34.37055072267925</v>
+        <v>33.75494497663782</v>
       </c>
     </row>
     <row r="31">
@@ -10368,7 +10368,7 @@
         </is>
       </c>
       <c r="C31">
-        <v>38.36347537032253</v>
+        <v>37.83783533605583</v>
       </c>
     </row>
     <row r="32">
@@ -10383,7 +10383,7 @@
         </is>
       </c>
       <c r="C32">
-        <v>47.64520736723398</v>
+        <v>47.08257216589515</v>
       </c>
     </row>
     <row r="33">
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="C33">
-        <v>30.66402268078223</v>
+        <v>30.27778372464798</v>
       </c>
     </row>
     <row r="34">
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="C34">
-        <v>39.74600589103538</v>
+        <v>39.24757045134573</v>
       </c>
     </row>
     <row r="35">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="C35">
-        <v>28.86995422984455</v>
+        <v>28.53269036525623</v>
       </c>
     </row>
     <row r="36">
@@ -10443,7 +10443,7 @@
         </is>
       </c>
       <c r="C36">
-        <v>28.14711412007461</v>
+        <v>27.86215322851367</v>
       </c>
     </row>
     <row r="37">
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="C37">
-        <v>39.66854222119643</v>
+        <v>38.99885603345047</v>
       </c>
     </row>
     <row r="38">
@@ -10473,7 +10473,7 @@
         </is>
       </c>
       <c r="C38">
-        <v>45.34839915363387</v>
+        <v>44.82306792659711</v>
       </c>
     </row>
     <row r="39">
@@ -10488,7 +10488,7 @@
         </is>
       </c>
       <c r="C39">
-        <v>27.00680589104332</v>
+        <v>26.57507930736779</v>
       </c>
     </row>
     <row r="40">
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="C40">
-        <v>41.67922369256501</v>
+        <v>41.15886138301373</v>
       </c>
     </row>
     <row r="41">
@@ -10518,7 +10518,7 @@
         </is>
       </c>
       <c r="C41">
-        <v>21.71493658086321</v>
+        <v>21.3813108471553</v>
       </c>
     </row>
     <row r="42">
@@ -10533,7 +10533,7 @@
         </is>
       </c>
       <c r="C42">
-        <v>48.19129352447257</v>
+        <v>47.22411699139989</v>
       </c>
     </row>
     <row r="43">
@@ -10548,7 +10548,7 @@
         </is>
       </c>
       <c r="C43">
-        <v>31.81801040014127</v>
+        <v>31.35766045589506</v>
       </c>
     </row>
     <row r="44">
@@ -10563,7 +10563,7 @@
         </is>
       </c>
       <c r="C44">
-        <v>41.90130733169551</v>
+        <v>41.42973355987387</v>
       </c>
     </row>
     <row r="45">
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="C45">
-        <v>31.53510281837602</v>
+        <v>30.9875295545985</v>
       </c>
     </row>
     <row r="46">
@@ -10593,7 +10593,7 @@
         </is>
       </c>
       <c r="C46">
-        <v>38.16586452970394</v>
+        <v>37.59443858883385</v>
       </c>
     </row>
     <row r="47">
@@ -10608,7 +10608,7 @@
         </is>
       </c>
       <c r="C47">
-        <v>27.94183611072752</v>
+        <v>27.47456443444379</v>
       </c>
     </row>
     <row r="48">
@@ -10623,7 +10623,7 @@
         </is>
       </c>
       <c r="C48">
-        <v>36.60418227648745</v>
+        <v>36.06859609991601</v>
       </c>
     </row>
     <row r="49">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="C49">
-        <v>35.59251471492991</v>
+        <v>35.07818112870507</v>
       </c>
     </row>
     <row r="50">
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="C50">
-        <v>39.43944411093926</v>
+        <v>38.82249670301957</v>
       </c>
     </row>
     <row r="51">
@@ -10668,7 +10668,7 @@
         </is>
       </c>
       <c r="C51">
-        <v>19.83335642665108</v>
+        <v>19.40669787966587</v>
       </c>
     </row>
     <row r="52">
@@ -10683,7 +10683,7 @@
         </is>
       </c>
       <c r="C52">
-        <v>30.26778016834878</v>
+        <v>29.74288286621121</v>
       </c>
     </row>
     <row r="53">
@@ -10698,7 +10698,7 @@
         </is>
       </c>
       <c r="C53">
-        <v>26.76418571869921</v>
+        <v>26.19707386979336</v>
       </c>
     </row>
     <row r="54">
@@ -10713,7 +10713,7 @@
         </is>
       </c>
       <c r="C54">
-        <v>21.70452816943379</v>
+        <v>21.14444414823692</v>
       </c>
     </row>
     <row r="55">
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="C55">
-        <v>26.78763204874603</v>
+        <v>26.30759634947111</v>
       </c>
     </row>
     <row r="56">
@@ -10743,7 +10743,7 @@
         </is>
       </c>
       <c r="C56">
-        <v>14.61785164370152</v>
+        <v>14.30529212770564</v>
       </c>
     </row>
     <row r="57">
@@ -10758,7 +10758,7 @@
         </is>
       </c>
       <c r="C57">
-        <v>46.26017565198951</v>
+        <v>45.33570716849891</v>
       </c>
     </row>
     <row r="58">
@@ -10773,7 +10773,7 @@
         </is>
       </c>
       <c r="C58">
-        <v>33.30886079618666</v>
+        <v>32.74771956203917</v>
       </c>
     </row>
     <row r="59">
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="C59">
-        <v>56.12512896531096</v>
+        <v>55.4344543452866</v>
       </c>
     </row>
     <row r="60">
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="C60">
-        <v>44.93578198376525</v>
+        <v>44.4711413374326</v>
       </c>
     </row>
     <row r="61">
@@ -10818,7 +10818,7 @@
         </is>
       </c>
       <c r="C61">
-        <v>36.62097245644279</v>
+        <v>36.10698320190033</v>
       </c>
     </row>
     <row r="62">
@@ -10833,7 +10833,7 @@
         </is>
       </c>
       <c r="C62">
-        <v>29.93956069031647</v>
+        <v>29.53775686568815</v>
       </c>
     </row>
     <row r="63">
@@ -10848,7 +10848,7 @@
         </is>
       </c>
       <c r="C63">
-        <v>15.94567341877486</v>
+        <v>15.68028677811165</v>
       </c>
     </row>
     <row r="64">
@@ -10863,7 +10863,7 @@
         </is>
       </c>
       <c r="C64">
-        <v>35.80492528665793</v>
+        <v>35.36732170676791</v>
       </c>
     </row>
     <row r="65">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="C65">
-        <v>22.7417335321488</v>
+        <v>22.00027366056602</v>
       </c>
     </row>
     <row r="66">
@@ -10893,7 +10893,7 @@
         </is>
       </c>
       <c r="C66">
-        <v>16.8602152144968</v>
+        <v>16.46987812274428</v>
       </c>
     </row>
     <row r="67">
@@ -10908,7 +10908,7 @@
         </is>
       </c>
       <c r="C67">
-        <v>35.99984187396467</v>
+        <v>35.32377090866756</v>
       </c>
     </row>
     <row r="68">
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="C68">
-        <v>16.69561257390728</v>
+        <v>16.25316576093141</v>
       </c>
     </row>
     <row r="69">
@@ -10938,7 +10938,7 @@
         </is>
       </c>
       <c r="C69">
-        <v>23.20450141981969</v>
+        <v>22.33322434816081</v>
       </c>
     </row>
     <row r="70">
@@ -10953,7 +10953,7 @@
         </is>
       </c>
       <c r="C70">
-        <v>20.57305290455586</v>
+        <v>20.02466439238577</v>
       </c>
     </row>
     <row r="71">
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="C71">
-        <v>34.79292282301629</v>
+        <v>33.91084351027875</v>
       </c>
     </row>
     <row r="72">
@@ -10983,7 +10983,7 @@
         </is>
       </c>
       <c r="C72">
-        <v>34.06564329310944</v>
+        <v>33.21445435216213</v>
       </c>
     </row>
     <row r="73">
@@ -10998,7 +10998,7 @@
         </is>
       </c>
       <c r="C73">
-        <v>10.96343246605272</v>
+        <v>10.62154259844766</v>
       </c>
     </row>
     <row r="74">
@@ -11013,7 +11013,7 @@
         </is>
       </c>
       <c r="C74">
-        <v>7.969572023574983</v>
+        <v>7.782668652160243</v>
       </c>
     </row>
     <row r="75">
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="C75">
-        <v>16.74537085623831</v>
+        <v>16.17444837136415</v>
       </c>
     </row>
     <row r="76">
@@ -11043,7 +11043,7 @@
         </is>
       </c>
       <c r="C76">
-        <v>29.87067839546477</v>
+        <v>29.10835215374552</v>
       </c>
     </row>
     <row r="77">
@@ -11058,7 +11058,7 @@
         </is>
       </c>
       <c r="C77">
-        <v>16.91498872609365</v>
+        <v>16.27938001938308</v>
       </c>
     </row>
     <row r="78">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="C78">
-        <v>39.54245235445715</v>
+        <v>38.62906150189742</v>
       </c>
     </row>
     <row r="79">
@@ -11088,7 +11088,7 @@
         </is>
       </c>
       <c r="C79">
-        <v>24.60595487784461</v>
+        <v>24.05635812904976</v>
       </c>
     </row>
     <row r="80">
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="C80">
-        <v>28.91965199581156</v>
+        <v>28.25213139230239</v>
       </c>
     </row>
     <row r="81">
@@ -11118,7 +11118,7 @@
         </is>
       </c>
       <c r="C81">
-        <v>21.61977225324352</v>
+        <v>21.10609330728778</v>
       </c>
     </row>
     <row r="82">
@@ -11133,7 +11133,7 @@
         </is>
       </c>
       <c r="C82">
-        <v>30.38060629001883</v>
+        <v>29.40162936936815</v>
       </c>
     </row>
     <row r="83">
@@ -11148,7 +11148,7 @@
         </is>
       </c>
       <c r="C83">
-        <v>12.70941514144465</v>
+        <v>12.36875269109519</v>
       </c>
     </row>
     <row r="84">
@@ -11163,7 +11163,7 @@
         </is>
       </c>
       <c r="C84">
-        <v>41.06654871542835</v>
+        <v>40.13635924028212</v>
       </c>
     </row>
     <row r="85">
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="C85">
-        <v>36.99648992657553</v>
+        <v>35.85289791285165</v>
       </c>
     </row>
     <row r="86">
@@ -11193,7 +11193,7 @@
         </is>
       </c>
       <c r="C86">
-        <v>24.45009777568204</v>
+        <v>23.67720609109429</v>
       </c>
     </row>
     <row r="87">
@@ -11208,7 +11208,7 @@
         </is>
       </c>
       <c r="C87">
-        <v>24.71441180559659</v>
+        <v>24.1043917514429</v>
       </c>
     </row>
     <row r="88">
@@ -11223,7 +11223,7 @@
         </is>
       </c>
       <c r="C88">
-        <v>52.97662653530515</v>
+        <v>51.87613995294066</v>
       </c>
     </row>
     <row r="89">
@@ -11238,7 +11238,7 @@
         </is>
       </c>
       <c r="C89">
-        <v>38.96394370949655</v>
+        <v>38.07796717189294</v>
       </c>
     </row>
     <row r="90">
@@ -11253,7 +11253,7 @@
         </is>
       </c>
       <c r="C90">
-        <v>23.84487039831377</v>
+        <v>23.0200033853911</v>
       </c>
     </row>
     <row r="91">
@@ -11268,7 +11268,7 @@
         </is>
       </c>
       <c r="C91">
-        <v>26.03918565573812</v>
+        <v>25.28632366281217</v>
       </c>
     </row>
     <row r="92">
@@ -11283,7 +11283,7 @@
         </is>
       </c>
       <c r="C92">
-        <v>25.36370339452061</v>
+        <v>24.84623514574021</v>
       </c>
     </row>
     <row r="93">
@@ -11298,7 +11298,7 @@
         </is>
       </c>
       <c r="C93">
-        <v>15.37613566725733</v>
+        <v>14.68360585458952</v>
       </c>
     </row>
     <row r="94">
@@ -11313,7 +11313,7 @@
         </is>
       </c>
       <c r="C94">
-        <v>29.66137073655472</v>
+        <v>28.99053523340854</v>
       </c>
     </row>
     <row r="95">
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="C95">
-        <v>21.10797206848373</v>
+        <v>20.62496469476384</v>
       </c>
     </row>
     <row r="96">
@@ -11343,7 +11343,7 @@
         </is>
       </c>
       <c r="C96">
-        <v>12.31488381482708</v>
+        <v>11.81995629532636</v>
       </c>
     </row>
     <row r="97">
@@ -11358,7 +11358,7 @@
         </is>
       </c>
       <c r="C97">
-        <v>26.06550270766389</v>
+        <v>25.18378146704233</v>
       </c>
     </row>
     <row r="98">
@@ -11373,7 +11373,7 @@
         </is>
       </c>
       <c r="C98">
-        <v>21.86709376479077</v>
+        <v>21.2213137716085</v>
       </c>
     </row>
     <row r="99">
@@ -11388,7 +11388,7 @@
         </is>
       </c>
       <c r="C99">
-        <v>56.91174655003424</v>
+        <v>55.71645006919081</v>
       </c>
     </row>
     <row r="100">
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="C100">
-        <v>19.4494897405777</v>
+        <v>18.61534360318008</v>
       </c>
     </row>
     <row r="101">
@@ -11418,7 +11418,7 @@
         </is>
       </c>
       <c r="C101">
-        <v>25.7404046871725</v>
+        <v>24.87606109496862</v>
       </c>
     </row>
     <row r="102">
@@ -11433,7 +11433,7 @@
         </is>
       </c>
       <c r="C102">
-        <v>39.20822070311088</v>
+        <v>38.50526962048674</v>
       </c>
     </row>
     <row r="103">
@@ -11448,7 +11448,7 @@
         </is>
       </c>
       <c r="C103">
-        <v>23.22997484491086</v>
+        <v>22.3454022062665</v>
       </c>
     </row>
     <row r="104">
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="C104">
-        <v>21.00803406083094</v>
+        <v>20.41731302633366</v>
       </c>
     </row>
     <row r="105">
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="C105">
-        <v>20.77715452642849</v>
+        <v>20.00415942702988</v>
       </c>
     </row>
     <row r="106">
@@ -11493,7 +11493,7 @@
         </is>
       </c>
       <c r="C106">
-        <v>39.97566362823648</v>
+        <v>39.0403313111988</v>
       </c>
     </row>
     <row r="107">
@@ -11508,7 +11508,7 @@
         </is>
       </c>
       <c r="C107">
-        <v>25.2190042862803</v>
+        <v>24.73678834546828</v>
       </c>
     </row>
     <row r="108">
@@ -11523,7 +11523,7 @@
         </is>
       </c>
       <c r="C108">
-        <v>29.09747088402708</v>
+        <v>28.19668867406861</v>
       </c>
     </row>
     <row r="109">
@@ -11538,7 +11538,7 @@
         </is>
       </c>
       <c r="C109">
-        <v>12.76292426989062</v>
+        <v>12.34855414156156</v>
       </c>
     </row>
     <row r="110">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="C110">
-        <v>27.88902870682065</v>
+        <v>27.2968076000766</v>
       </c>
     </row>
     <row r="111">
@@ -11568,7 +11568,7 @@
         </is>
       </c>
       <c r="C111">
-        <v>25.46757510230898</v>
+        <v>24.74929387641738</v>
       </c>
     </row>
     <row r="112">
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="C112">
-        <v>11.80556463739358</v>
+        <v>11.32106377510243</v>
       </c>
     </row>
     <row r="113">
@@ -11598,7 +11598,7 @@
         </is>
       </c>
       <c r="C113">
-        <v>39.3487605731198</v>
+        <v>38.6779526640965</v>
       </c>
     </row>
     <row r="114">
@@ -11613,7 +11613,7 @@
         </is>
       </c>
       <c r="C114">
-        <v>18.15335844244948</v>
+        <v>17.46522941528066</v>
       </c>
     </row>
     <row r="115">
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="C115">
-        <v>34.02997538438925</v>
+        <v>33.28622787292586</v>
       </c>
     </row>
     <row r="116">
@@ -11643,7 +11643,7 @@
         </is>
       </c>
       <c r="C116">
-        <v>32.71684271846188</v>
+        <v>32.14303518820611</v>
       </c>
     </row>
     <row r="117">
@@ -11658,7 +11658,7 @@
         </is>
       </c>
       <c r="C117">
-        <v>36.42309241970267</v>
+        <v>35.80329102007341</v>
       </c>
     </row>
     <row r="118">
@@ -11673,7 +11673,7 @@
         </is>
       </c>
       <c r="C118">
-        <v>7.030525483221525</v>
+        <v>6.757740060888698</v>
       </c>
     </row>
     <row r="119">
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="C119">
-        <v>18.83582962865379</v>
+        <v>18.21229704246289</v>
       </c>
     </row>
     <row r="120">
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="C120">
-        <v>20.84774351157882</v>
+        <v>20.37782248159677</v>
       </c>
     </row>
     <row r="121">
@@ -11718,7 +11718,7 @@
         </is>
       </c>
       <c r="C121">
-        <v>20.64031541564402</v>
+        <v>20.20620990733237</v>
       </c>
     </row>
     <row r="122">
@@ -11733,7 +11733,7 @@
         </is>
       </c>
       <c r="C122">
-        <v>47.02820160443556</v>
+        <v>46.07573446289673</v>
       </c>
     </row>
     <row r="123">
@@ -11748,7 +11748,7 @@
         </is>
       </c>
       <c r="C123">
-        <v>27.16603170315223</v>
+        <v>26.3548639993495</v>
       </c>
     </row>
     <row r="124">
@@ -11763,7 +11763,7 @@
         </is>
       </c>
       <c r="C124">
-        <v>32.2471799147256</v>
+        <v>31.57949128308851</v>
       </c>
     </row>
     <row r="125">
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="C125">
-        <v>23.18245701507416</v>
+        <v>22.67509996788293</v>
       </c>
     </row>
     <row r="126">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="C126">
-        <v>21.29972454452716</v>
+        <v>20.54870208919165</v>
       </c>
     </row>
     <row r="127">
@@ -11808,7 +11808,7 @@
         </is>
       </c>
       <c r="C127">
-        <v>36.83350895420893</v>
+        <v>36.0808672410994</v>
       </c>
     </row>
     <row r="128">
@@ -11823,7 +11823,7 @@
         </is>
       </c>
       <c r="C128">
-        <v>16.40526740598066</v>
+        <v>15.67535986341749</v>
       </c>
     </row>
     <row r="129">
@@ -11838,7 +11838,7 @@
         </is>
       </c>
       <c r="C129">
-        <v>40.84166261694882</v>
+        <v>40.11378823216777</v>
       </c>
     </row>
     <row r="130">
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="C130">
-        <v>30.97555630635593</v>
+        <v>30.44883651869334</v>
       </c>
     </row>
     <row r="131">
@@ -11868,7 +11868,7 @@
         </is>
       </c>
       <c r="C131">
-        <v>33.04784603373193</v>
+        <v>32.53221043689534</v>
       </c>
     </row>
     <row r="132">
@@ -11883,7 +11883,7 @@
         </is>
       </c>
       <c r="C132">
-        <v>49.3457184924102</v>
+        <v>48.65647028814254</v>
       </c>
     </row>
   </sheetData>

--- a/01_Preprocess/01_Filtering/c_data/01_filter.xlsx
+++ b/01_Preprocess/01_Filtering/c_data/01_filter.xlsx
@@ -7,9 +7,11 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="overview" sheetId="1" r:id="rId1"/>
-    <sheet name="filter_log" sheetId="2" r:id="rId2"/>
-    <sheet name="contaminants_removed" sheetId="3" r:id="rId3"/>
+    <sheet name="samples" sheetId="1" r:id="rId1"/>
+    <sheet name="filtering_summary" sheetId="2" r:id="rId2"/>
+    <sheet name="annotation_exclusions" sheetId="3" r:id="rId3"/>
+    <sheet name="removed_contaminants" sheetId="4" r:id="rId4"/>
+    <sheet name="sample_contamination" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -353,64 +355,5550 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>sheet</t>
+          <t>sample_id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>rows</t>
+          <t>participant</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>columns</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>timepoint</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>sex</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>filter_log</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
+          <t>S02_L_T1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rows, groups and signal after each filter</t>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CL_MDR_2E-T1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>contaminants_removed</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>211</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
+          <t>S02_L_T2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Removed contaminants and their signal</t>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CL_MDR_2E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>S02_R_T1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CL_MR_2D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>S02_R_T2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CL_MR_2D_T2r</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S03_L_T1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CL_MDR_3E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S03_L_T2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CL_MDR_3E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S03_R_T1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CL_MDR_3D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>S03_R_T2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>CL_MDR_3D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S04_L_T1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CL_MDR_4E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S04_L_T2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CL_MDR_4E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S04_R_T1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>CL_MDR_4D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S04_R_T2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>CL_MDR_4D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S05_L_T1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>CL_MDR_5E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>S05_L_T2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>CL_MDR_5E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S05_R_T1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>CL_MDR_5D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S05_R_T2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>CL_MDR_5D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S06_L_T1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>CL_MDR_6E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S06_R_T1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>CL_MR_6D_T1r</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S06_R_T2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>CL_MR_6D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S07_L_T1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>CL_MR_7E_T1r</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S07_L_T2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>CL_MDR_7E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>S07_R_T1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CL_MDR_7D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>S07_R_T2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>CL_MDR_7D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>S08_L_T1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>CL_MDR_8E-T1r</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>S08_L_T2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>CL_MDR_8E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>S08_R_T1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>CL_MDR_8D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>S08_R_T2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>CL_MR_8D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S09_L_T1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>CL_MDR_9E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S09_L_T2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>CL_MDR_9E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>S09_R_T1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>CL_MDR_9D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>S09_R_T2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>CL_MDR_9D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>S10_L_T1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>CL_MDR_10E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>S10_L_T2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>CL_MDR_10E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>S10_R_T1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>CL_MDR_10D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>S10_R_T2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>CL_MDR_10D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>S11_L_T1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>CL_MDR_11E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>S11_L_T2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>CL_MDR_11E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>S11_R_T1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>CL_MDR_11D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>S11_R_T2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>CL_MDR_11D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>S12_L_T1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>CL_MDR_12E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>S12_L_T2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>CL_MDR_12E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>S12_R_T1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>CL_MDR_12D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>S12_R_T2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>CL_MDR_12D-T2rR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>S13_L_T1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>CL_MDR_13E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>S13_L_T2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>CL_MDR_13E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>S13_R_T1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>CL_MDR_13D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>S13_R_T2</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>CL_MDR_13D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>S14_L_T1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>CL_MDR_14E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>S14_L_T2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>CL_MDR_14E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>S14_R_T1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>CL_MDR_14D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>S14_R_T2</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>CL_MDR_14D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>S15_L_T1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>CL_MDR_15E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>S15_L_T2</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>CL_MDR_15E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>S15_R_T1</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>CL_MDR_15D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>S15_R_T2</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>CL_MDR_15D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>S16_L_T1</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>CL_MR_16E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>S16_L_T2</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>CL_MR_16E_T2r</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>S16_R_T1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>CL_MDR_16D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>S16_R_T2</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>CL_MDR_16D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>S17_L_T1</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>CL_MDR_17E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S17_L_T2</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>CL_MDR_17E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>S17_R_T1</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>CL_MDR_17D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>S17_R_T2</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>CL_MDR_17D-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>S18_L_T1</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>S18</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>CL_MDR_18E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>S18_L_T2</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>S18</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>CL_MDR_18E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>S18_R_T1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>S18</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>CL_MDR_18D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>S18_R_T2</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>S18</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>CL_MDR_18D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>S20_L_T1</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>CL_MDR_20E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>S20_L_T2</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>CL_MDR_20E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>S20_R_T1</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>CL_MDR_20D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>S20_R_T2</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>CL_MDR_20D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>S21_L_T1</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>S21</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>CL_MDR_21E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>S21_L_T2</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>S21</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>CL_MDR_21E_T2r</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>S21_R_T1</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>S21</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>CL_MDR_21D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>S21_R_T2</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>S21</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>CL_MDR_21D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>S23_L_T1</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>S23</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>CL_MDR_23E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>S23_L_T2</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>S23</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>CL_MDR_23E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>S23_R_T1</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>S23</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>CL_MDR_23D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>S23_R_T2</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>S23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>CL_MDR_23D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>S24_L_T1</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>S24</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>CL_MDR_24E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>S24_L_T2</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>S24</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>CL_MDR_24E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>S24_R_T1</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>S24</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>CL_MDR_24D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>S24_R_T2</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>S24</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>CL_MDR_24D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>S25_L_T1</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>CL_MDR_25E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>S25_L_T2</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>CL_MDR_25E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>S25_R_T1</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>CL_MDR_25D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>S25_R_T2</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>CL_MDR_25D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>S26_L_T1</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>S26</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>CL_MDR_26E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>S26_L_T2</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>S26</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>CL_MDR_26E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>S26_R_T1</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>S26</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>CL_MDR_26D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>S26_R_T2</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>S26</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>CL_MDR_26D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>S27_L_T1</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>S27</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>CL_MDR_27E_T1r</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>S27_L_T2</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>S27</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>CL_MDR_27E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>S27_R_T1</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>S27</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>CL_MDR_27D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>S27_R_T2</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>S27</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>CL_MDR_27D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>S28_L_T1</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>S28</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>CL_MDR_28E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>S28_L_T2</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>S28</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>CL_MDR_28E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>S28_R_T1</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>S28</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>CL_MDR_28D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>S28_R_T2</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>S28</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>CL_MDR_28D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>S29_L_T1</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>CL_MDR_29E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>S29_L_T2</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>CL_MDR_29E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>S29_R_T1</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>CL_MDR_29D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>S29_R_T2</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>CL_MDR_29D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>S30_L_T1</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>S30</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>CL_MDR_30E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>S30_L_T2</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>S30</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>CL_MDR_30E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>S30_R_T1</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>S30</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>CL_MDR_30D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>S30_R_T2</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>S30</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>CL_MDR_30D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>S31_L_T1</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>S31</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>CL_MDR_31E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>S31_L_T2</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>S31</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>CL_MDR_31E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>S31_R_T1</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>S31</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>CL_MDR_31D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>S31_R_T2</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>S31</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>CL_MDR_31D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>S32_L_T1</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>CL_MDR_32E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>S32_L_T2</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>CL_MDR_32E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>S32_R_T1</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>CL_MDR_32D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>S32_R_T2</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>CL_MDR_32D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>S33_L_T1</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>S33</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>CL_MDR_33E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>S33_L_T2</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>S33</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>CL_MDR_33E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>S33_R_T1</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>S33</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>CL_MDR_33D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>S33_R_T2</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>S33</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>CL_MDR_33D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>S35_L_T1</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>S35</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>CL_MDR_35E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>S35_L_T2</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>S35</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>CL_MDR_35E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>S35_R_T1</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>S35</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>CL_MDR_35D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>S35_R_T2</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>S35</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>CL_MDR_35D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>S36_L_T1</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>S36</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>CL_MDR_36E_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>S36_L_T2</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>S36</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>CL_MDR_36E_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>S36_R_T1</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>S36</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>CL_MDR_36D_T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>S36_R_T2</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>S36</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>CL_MDR_36D_T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>S37_L_T1</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>S37</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>CL_MDR_37E-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>S37_L_T2</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>S37</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>CL_MDR_37E-T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>S37_R_T1</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>S37</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>CL_MDR_37D-T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>S37_R_T2</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>S37</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>HLRT</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>CL_MDR_37D-T2</t>
         </is>
       </c>
     </row>
@@ -453,13 +5941,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>53760</v>
+        <v>53744</v>
       </c>
       <c r="C2">
-        <v>3736</v>
+        <v>3734</v>
       </c>
       <c r="D2">
-        <v>99.72765070997796</v>
+        <v>98.58844075613163</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +5957,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>49801</v>
+        <v>49871</v>
       </c>
       <c r="C3">
         <v>3664</v>
       </c>
       <c r="D3">
-        <v>85.94764178778486</v>
+        <v>87.63098062339989</v>
       </c>
     </row>
     <row r="4">
@@ -485,13 +5973,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>49788</v>
+        <v>49858</v>
       </c>
       <c r="C4">
         <v>3662</v>
       </c>
       <c r="D4">
-        <v>85.94736147006761</v>
+        <v>87.63070030568271</v>
       </c>
     </row>
     <row r="5">
@@ -501,13 +5989,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>47133</v>
+        <v>47201</v>
       </c>
       <c r="C5">
         <v>3451</v>
       </c>
       <c r="D5">
-        <v>57.99577454956071</v>
+        <v>59.67866240498889</v>
       </c>
     </row>
   </sheetData>
@@ -517,6 +6005,72 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>precursors</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>pct_signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>cRAP-only group</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>89</v>
+      </c>
+      <c r="C2">
+        <v>1.410501914983034</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>reversed decoy</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>19</v>
+      </c>
+      <c r="C3">
+        <v>0.001057328886625115</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mentions cRAP at all</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>1258</v>
+      </c>
+      <c r="C4">
+        <v>64.79051964118159</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D212"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -932,10 +6486,10 @@
         </is>
       </c>
       <c r="C23">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D23">
-        <v>0.006134026491755945</v>
+        <v>0.006253658895711615</v>
       </c>
     </row>
     <row r="24">
@@ -1157,7 +6711,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IGHG3</t>
+          <t>KRT10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1166,46 +6720,46 @@
         </is>
       </c>
       <c r="C36">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D36">
-        <v>0.002033071723152557</v>
+        <v>0.002113686068996637</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>APOH</t>
+          <t>IGHG3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C37">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D37">
-        <v>0.001834766275260182</v>
+        <v>0.002033071723152557</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KRT10</t>
+          <t>APOH</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="C38">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D38">
-        <v>0.001782338284746402</v>
+        <v>0.001834766275260182</v>
       </c>
     </row>
     <row r="39">
@@ -4338,6 +9892,1998 @@
       </c>
       <c r="D212">
         <v>3.635119439611477E-08</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C132"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>sample_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>pct_signal_removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>S02_L_T1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>47.02304114647254</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>S02_L_T2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>32.55712075226026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>S02_R_T1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>26.36469023306657</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>S02_R_T2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>43.53350247764178</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S03_L_T1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>32.39487348948416</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S03_L_T2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>33.31482870417345</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S03_R_T1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>25.91978552525977</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>S03_R_T2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>29.72067622593642</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S04_L_T1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>23.00692063974904</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S04_L_T2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>23.33137910666068</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S04_R_T1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>79.41277992510496</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S04_R_T2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>47.01711075034413</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S05_L_T1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>43.16364657622505</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>S05_L_T2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>20.78960794558883</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S05_R_T1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>22.41970779267011</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S05_R_T2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>41.51855872401673</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S06_L_T1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>23.12442177215729</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S06_R_T1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>28.8023231470601</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S06_R_T2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>21.81614435383804</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S07_L_T1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>19.76410868241904</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S07_L_T2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>27.665080911571</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>S07_R_T1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>20.74119469340042</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>S07_R_T2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>23.44822584218077</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>S08_L_T1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>32.33712726566275</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>S08_L_T2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>30.61677370438202</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>S08_R_T1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>27.94241417164917</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>S08_R_T2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>16.1899190370299</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S09_L_T1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>41.79544804452135</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S09_L_T2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>33.75494497663782</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>S09_R_T1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>37.83783533605583</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>S09_R_T2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>47.08257216589515</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>S10_L_T1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>30.27778372464798</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>S10_L_T2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>39.24757045134573</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>S10_R_T1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>28.53269036525623</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>S10_R_T2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>27.86215322851367</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>S11_L_T1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>38.99885603345047</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>S11_L_T2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>44.82306792659711</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>S11_R_T1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>26.57507930736779</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>S11_R_T2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>41.15886138301373</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>S12_L_T1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>21.3813108471553</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>S12_L_T2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>47.22411699139989</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>S12_R_T1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>31.35766045589506</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>S12_R_T2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>41.42973355987387</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>S13_L_T1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>30.9875295545985</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>S13_L_T2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>37.59443858883385</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>S13_R_T1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>27.47456443444379</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>S13_R_T2</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>36.06859609991601</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>S14_L_T1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>35.07818112870507</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>S14_L_T2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>38.82249670301957</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>S14_R_T1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>19.40669787966587</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>S14_R_T2</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>29.74288286621121</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>S15_L_T1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>26.19707386979336</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>S15_L_T2</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>21.14444414823692</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>S15_R_T1</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>26.30759634947111</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>S15_R_T2</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>14.30529212770564</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>S16_L_T1</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>45.33570716849891</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>S16_L_T2</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>32.74771956203917</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>S16_R_T1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>55.4344543452866</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>S16_R_T2</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>44.4711413374326</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>S17_L_T1</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>36.10698320190033</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S17_L_T2</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>29.53775686568815</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>S17_R_T1</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>15.68028677811165</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>S17_R_T2</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>35.36732170676791</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>S18_L_T1</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>22.00027366056602</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>S18_L_T2</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>16.46987812274428</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>S18_R_T1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>35.32377090866756</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>S18_R_T2</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>16.25316576093141</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>S20_L_T1</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>22.33322434816081</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>S20_L_T2</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>20.02466439238577</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>S20_R_T1</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>33.91084351027875</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>S20_R_T2</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>33.21445435216213</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>S21_L_T1</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>10.62154259844766</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>S21_L_T2</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>7.782668652160243</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>S21_R_T1</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>16.17444837136415</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>S21_R_T2</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>29.10835215374552</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>S23_L_T1</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>16.27938001938308</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>S23_L_T2</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>38.62906150189742</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>S23_R_T1</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>24.05635812904976</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>S23_R_T2</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>28.25213139230239</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>S24_L_T1</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>21.10609330728778</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>S24_L_T2</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>29.40162936936815</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>S24_R_T1</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>12.36875269109519</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>S24_R_T2</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>40.13635924028212</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>S25_L_T1</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>35.85289791285165</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>S25_L_T2</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>23.67720609109429</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>S25_R_T1</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>24.1043917514429</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>S25_R_T2</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>51.87613995294066</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>S26_L_T1</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>38.07796717189294</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>S26_L_T2</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>23.0200033853911</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>S26_R_T1</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>25.28632366281217</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>S26_R_T2</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>24.84623514574021</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>S27_L_T1</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>14.68360585458952</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>S27_L_T2</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>28.99053523340854</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>S27_R_T1</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>20.62496469476384</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>S27_R_T2</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>11.81995629532636</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>S28_L_T1</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>25.18378146704233</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>S28_L_T2</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>21.2213137716085</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>S28_R_T1</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>55.71645006919081</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>S28_R_T2</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>18.61534360318008</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>S29_L_T1</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>24.87606109496862</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>S29_L_T2</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>38.50526962048674</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>S29_R_T1</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>22.3454022062665</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>S29_R_T2</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>20.41731302633366</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>S30_L_T1</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>20.00415942702988</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>S30_L_T2</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>39.0403313111988</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>S30_R_T1</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>24.73678834546828</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>S30_R_T2</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>28.19668867406861</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>S31_L_T1</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>12.34855414156156</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>S31_L_T2</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>27.2968076000766</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>S31_R_T1</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>24.74929387641738</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>S31_R_T2</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>11.32106377510243</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>S32_L_T1</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>38.6779526640965</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>S32_L_T2</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>17.46522941528066</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>S32_R_T1</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>33.28622787292586</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>S32_R_T2</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>32.14303518820611</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>S33_L_T1</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>35.80329102007341</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>S33_L_T2</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>6.757740060888698</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>S33_R_T1</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>18.21229704246289</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>S33_R_T2</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>20.37782248159677</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>S35_L_T1</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>20.20620990733237</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>S35_L_T2</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>46.07573446289673</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>S35_R_T1</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>26.3548639993495</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>S35_R_T2</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>31.57949128308851</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>S36_L_T1</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>22.67509996788293</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>S36_L_T2</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>20.54870208919165</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>S36_R_T1</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>36.0808672410994</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>S36_R_T2</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>15.67535986341749</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>S37_L_T1</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>BFR_T1</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>40.11378823216777</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>S37_L_T2</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>BFR_T2</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>30.44883651869334</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>S37_R_T1</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>HLRT_T1</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>32.53221043689534</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>S37_R_T2</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>HLRT_T2</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>48.65647028814254</v>
       </c>
     </row>
   </sheetData>
